--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5FE560-BB79-482C-92F2-23037F838D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -83,13 +89,22 @@
   </si>
   <si>
     <t>Custo</t>
+  </si>
+  <si>
+    <t>Renner_Locator</t>
+  </si>
+  <si>
+    <t>::</t>
+  </si>
+  <si>
+    <t>%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,24 +156,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +223,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,6 +257,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,9 +292,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -439,11 +468,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -512,6 +541,994 @@
       </c>
       <c r="W1" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>1018</v>
+      </c>
+      <c r="D2">
+        <v>1031</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2">
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B3">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>1018</v>
+      </c>
+      <c r="D3">
+        <v>1031</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>3.4722222222222222E-5</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1875</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
+        <v>25</v>
+      </c>
+      <c r="V3" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3">
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B4">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1018</v>
+      </c>
+      <c r="D4">
+        <v>1031</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>245</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>46179</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1018</v>
+      </c>
+      <c r="D5">
+        <v>1031</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5">
+        <v>245</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" t="s">
+        <v>25</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="s">
+        <v>25</v>
+      </c>
+      <c r="W5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1018</v>
+      </c>
+      <c r="D6">
+        <v>1031</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>111780</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
+        <v>25</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="s">
+        <v>25</v>
+      </c>
+      <c r="V6" t="s">
+        <v>25</v>
+      </c>
+      <c r="W6">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>1018</v>
+      </c>
+      <c r="D7">
+        <v>1031</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>111780</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0.73329999999999995</v>
+      </c>
+      <c r="R7" s="4">
+        <v>0.2727</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="4">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>0.25800000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1018</v>
+      </c>
+      <c r="D8">
+        <v>1031</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8">
+        <v>111780</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>631</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="P8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" t="s">
+        <v>25</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="s">
+        <v>25</v>
+      </c>
+      <c r="V8" s="4">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1.4870000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B9">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1018</v>
+      </c>
+      <c r="D9">
+        <v>1031</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9">
+        <v>111780</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>22666</v>
+      </c>
+      <c r="J9">
+        <v>404</v>
+      </c>
+      <c r="K9">
+        <v>26</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>25</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P9" s="3">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>1.78E-2</v>
+      </c>
+      <c r="R9" s="4">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9" s="4">
+        <v>3.85E-2</v>
+      </c>
+      <c r="V9" s="4">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>45.74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1018</v>
+      </c>
+      <c r="D10">
+        <v>1031</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10">
+        <v>111780</v>
+      </c>
+      <c r="G10">
+        <v>20</v>
+      </c>
+      <c r="H10">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <v>36808</v>
+      </c>
+      <c r="J10">
+        <v>722</v>
+      </c>
+      <c r="K10">
+        <v>54</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>54</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P10" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="R10" s="4">
+        <v>7.4800000000000005E-2</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="4">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>86.513999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>1018</v>
+      </c>
+      <c r="D11">
+        <v>1031</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11">
+        <v>111780</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <v>36828</v>
+      </c>
+      <c r="J11">
+        <v>1017</v>
+      </c>
+      <c r="K11">
+        <v>74</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>74</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" s="3">
+        <v>3.4722222222222224E-4</v>
+      </c>
+      <c r="P11" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>2.76E-2</v>
+      </c>
+      <c r="R11" s="4">
+        <v>7.2800000000000004E-2</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="4">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>106.19499999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B12">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>1018</v>
+      </c>
+      <c r="D12">
+        <v>1031</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12">
+        <v>111780</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>32542</v>
+      </c>
+      <c r="J12">
+        <v>608</v>
+      </c>
+      <c r="K12">
+        <v>39</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>39</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P12" s="3">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="R12" s="4">
+        <v>6.4100000000000004E-2</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>72.512</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B13">
+        <v>15</v>
+      </c>
+      <c r="C13">
+        <v>1018</v>
+      </c>
+      <c r="D13">
+        <v>1031</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13">
+        <v>111780</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>43740</v>
+      </c>
+      <c r="J13">
+        <v>817</v>
+      </c>
+      <c r="K13">
+        <v>41</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>41</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P13" s="3">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="R13" s="4">
+        <v>5.0200000000000002E-2</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>92.697999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B14">
+        <v>16</v>
+      </c>
+      <c r="C14">
+        <v>1018</v>
+      </c>
+      <c r="D14">
+        <v>1031</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14">
+        <v>111780</v>
+      </c>
+      <c r="G14">
+        <v>20</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>28282</v>
+      </c>
+      <c r="J14">
+        <v>567</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>20</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="R14" s="4">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>73.197999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B15">
+        <v>17</v>
+      </c>
+      <c r="C15">
+        <v>1018</v>
+      </c>
+      <c r="D15">
+        <v>1031</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15">
+        <v>111780</v>
+      </c>
+      <c r="G15">
+        <v>18</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>24084</v>
+      </c>
+      <c r="J15">
+        <v>51</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>4.9768518518518521E-3</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1.9444444444444444E-3</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="R15" s="4">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>78.960999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5FE560-BB79-482C-92F2-23037F838D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CA1E5D-1348-4350-915B-FC9C1DD5F4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,8 +469,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1529,6 +1554,219 @@
       </c>
       <c r="W15">
         <v>78.960999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>1018</v>
+      </c>
+      <c r="D16">
+        <v>1031</v>
+      </c>
+      <c r="E16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16">
+        <v>61467</v>
+      </c>
+      <c r="G16">
+        <v>20</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>23703</v>
+      </c>
+      <c r="J16">
+        <v>388</v>
+      </c>
+      <c r="K16">
+        <v>28</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>27</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="P16" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="R16" s="4">
+        <v>7.22E-2</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16" s="4">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="V16" s="4">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>62.215000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B17">
+        <v>9</v>
+      </c>
+      <c r="C17">
+        <v>1018</v>
+      </c>
+      <c r="D17">
+        <v>1031</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>61467</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>31364</v>
+      </c>
+      <c r="J17">
+        <v>333</v>
+      </c>
+      <c r="K17">
+        <v>18</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>18</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" s="3">
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="P17" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>1.06E-2</v>
+      </c>
+      <c r="R17" s="4">
+        <v>5.4100000000000002E-2</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>48.186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>1018</v>
+      </c>
+      <c r="D18">
+        <v>1031</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18">
+        <v>61467</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>43731</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
+      <c r="R18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18" t="s">
+        <v>25</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18" t="s">
+        <v>25</v>
+      </c>
+      <c r="V18" s="4">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>67.918000000000006</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CA1E5D-1348-4350-915B-FC9C1DD5F4AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99D34BB-C409-49D7-A81A-7ABAD448C547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1653,34 +1653,34 @@
         <v>2</v>
       </c>
       <c r="I17">
-        <v>31364</v>
+        <v>31434</v>
       </c>
       <c r="J17">
-        <v>333</v>
+        <v>403</v>
       </c>
       <c r="K17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
       <c r="O17" s="3">
-        <v>8.3333333333333339E-4</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="P17" s="3">
-        <v>8.564814814814815E-4</v>
+        <v>7.5231481481481482E-4</v>
       </c>
       <c r="Q17" s="4">
-        <v>1.06E-2</v>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="R17" s="4">
-        <v>5.4100000000000002E-2</v>
+        <v>5.21E-2</v>
       </c>
       <c r="S17" s="5">
         <v>0</v>
@@ -1718,55 +1718,339 @@
         <v>61467</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>43731</v>
+        <v>44193</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
-      <c r="O18" t="s">
-        <v>24</v>
-      </c>
-      <c r="P18" t="s">
-        <v>24</v>
+      <c r="O18" s="3">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="P18" s="3">
+        <v>7.0601851851851847E-4</v>
       </c>
       <c r="Q18" s="5">
-        <v>0</v>
-      </c>
-      <c r="R18" t="s">
-        <v>25</v>
-      </c>
-      <c r="S18" t="s">
-        <v>25</v>
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="R18" s="4">
+        <v>7.5800000000000006E-2</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
       </c>
       <c r="T18">
         <v>0</v>
       </c>
-      <c r="U18" t="s">
-        <v>25</v>
+      <c r="U18" s="5">
+        <v>0</v>
       </c>
       <c r="V18" s="4">
         <v>1</v>
       </c>
       <c r="W18">
-        <v>67.918000000000006</v>
+        <v>68.828000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B19">
+        <v>11</v>
+      </c>
+      <c r="C19">
+        <v>1018</v>
+      </c>
+      <c r="D19">
+        <v>1031</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19">
+        <v>61467</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>35504</v>
+      </c>
+      <c r="J19">
+        <v>487</v>
+      </c>
+      <c r="K19">
+        <v>22</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>22</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="P19" s="3">
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>1.37E-2</v>
+      </c>
+      <c r="R19" s="4">
+        <v>4.5199999999999997E-2</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>65.052000000000007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>1018</v>
+      </c>
+      <c r="D20">
+        <v>1031</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20">
+        <v>61467</v>
+      </c>
+      <c r="G20">
+        <v>20</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>28979</v>
+      </c>
+      <c r="J20">
+        <v>584</v>
+      </c>
+      <c r="K20">
+        <v>20</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>20</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P20" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="R20" s="4">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="4">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>77.728999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21">
+        <v>1018</v>
+      </c>
+      <c r="D21">
+        <v>1031</v>
+      </c>
+      <c r="E21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>61467</v>
+      </c>
+      <c r="G21">
+        <v>20</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>40920</v>
+      </c>
+      <c r="J21">
+        <v>953</v>
+      </c>
+      <c r="K21">
+        <v>46</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>45</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="P21" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="R21" s="4">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="S21" s="4">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>106.718</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B22">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>1018</v>
+      </c>
+      <c r="D22">
+        <v>1031</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22">
+        <v>61467</v>
+      </c>
+      <c r="G22">
+        <v>20</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <v>21787</v>
+      </c>
+      <c r="J22">
+        <v>181</v>
+      </c>
+      <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>8</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" s="3">
+        <v>1.261574074074074E-3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="R22" s="4">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>41.500999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99D34BB-C409-49D7-A81A-7ABAD448C547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FFA696-528A-4601-87B8-426B6442DD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2008,34 +2008,34 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <v>21787</v>
+        <v>21985</v>
       </c>
       <c r="J22">
-        <v>181</v>
+        <v>379</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N22">
         <v>1</v>
       </c>
       <c r="O22" s="3">
-        <v>1.261574074074074E-3</v>
+        <v>6.018518518518519E-4</v>
       </c>
       <c r="P22" s="3">
-        <v>5.9027777777777778E-4</v>
+        <v>4.6296296296296298E-4</v>
       </c>
       <c r="Q22" s="4">
-        <v>8.3000000000000001E-3</v>
+        <v>1.72E-2</v>
       </c>
       <c r="R22" s="4">
-        <v>4.4200000000000003E-2</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="S22" s="5">
         <v>0</v>
@@ -2051,6 +2051,219 @@
       </c>
       <c r="W22">
         <v>41.500999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+      <c r="C23">
+        <v>1018</v>
+      </c>
+      <c r="D23">
+        <v>1031</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23">
+        <v>61467</v>
+      </c>
+      <c r="G23">
+        <v>20</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>35725</v>
+      </c>
+      <c r="J23">
+        <v>567</v>
+      </c>
+      <c r="K23">
+        <v>29</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>29</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="P23" s="3">
+        <v>3.0092592592592595E-4</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="R23" s="4">
+        <v>5.11E-2</v>
+      </c>
+      <c r="S23" s="5">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>63.183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B24">
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <v>1018</v>
+      </c>
+      <c r="D24">
+        <v>1031</v>
+      </c>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24">
+        <v>61467</v>
+      </c>
+      <c r="G24">
+        <v>20</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>25853</v>
+      </c>
+      <c r="J24">
+        <v>290</v>
+      </c>
+      <c r="K24">
+        <v>8</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>7</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="P24" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>1.12E-2</v>
+      </c>
+      <c r="R24" s="4">
+        <v>2.76E-2</v>
+      </c>
+      <c r="S24" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>69.637</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B25">
+        <v>17</v>
+      </c>
+      <c r="C25">
+        <v>1018</v>
+      </c>
+      <c r="D25">
+        <v>1031</v>
+      </c>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25">
+        <v>61467</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>26158</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="s">
+        <v>24</v>
+      </c>
+      <c r="P25" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="5">
+        <v>0</v>
+      </c>
+      <c r="R25" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25" t="s">
+        <v>25</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25" t="s">
+        <v>25</v>
+      </c>
+      <c r="V25" s="4">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>99.117000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01FFA696-528A-4601-87B8-426B6442DD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99967EF-A6B5-4A25-95F8-2C72397F7C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -2144,43 +2144,43 @@
         <v>61467</v>
       </c>
       <c r="G24">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>25853</v>
+        <v>26031</v>
       </c>
       <c r="J24">
-        <v>290</v>
+        <v>468</v>
       </c>
       <c r="K24">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
       <c r="M24">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>9.3749999999999997E-4</v>
+        <v>5.7870370370370367E-4</v>
       </c>
       <c r="P24" s="3">
-        <v>4.3981481481481481E-4</v>
+        <v>4.861111111111111E-4</v>
       </c>
       <c r="Q24" s="4">
-        <v>1.12E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="R24" s="4">
-        <v>2.76E-2</v>
+        <v>3.6299999999999999E-2</v>
       </c>
       <c r="S24" s="4">
-        <v>0.125</v>
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="T24">
         <v>0</v>
@@ -2215,49 +2215,49 @@
         <v>61467</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>26158</v>
+        <v>26657</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>24</v>
-      </c>
-      <c r="P25" t="s">
-        <v>24</v>
+      <c r="O25" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="P25" s="3">
+        <v>1.4120370370370369E-3</v>
       </c>
       <c r="Q25" s="5">
-        <v>0</v>
-      </c>
-      <c r="R25" t="s">
-        <v>25</v>
-      </c>
-      <c r="S25" t="s">
-        <v>25</v>
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="R25" s="4">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="S25" s="5">
+        <v>0</v>
       </c>
       <c r="T25">
         <v>0</v>
       </c>
-      <c r="U25" t="s">
-        <v>25</v>
+      <c r="U25" s="5">
+        <v>0</v>
       </c>
       <c r="V25" s="4">
         <v>1</v>

--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99967EF-A6B5-4A25-95F8-2C72397F7C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75234F04-E605-4050-B3F3-584890905B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -2269,4 +2270,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35981261-B62C-4B92-BA64-8BAF4ABE5A4C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\Backup\OSPDataCommandCenter_MULTI_CLIENTES_BG_PADRAO\OSPDataCommandCenter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75234F04-E605-4050-B3F3-584890905B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15537A2-5D06-4656-BBF9-71821FDA1301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
+    <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -2279,4 +2280,13 @@
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBB257C1-6D55-4FB3-9A7E-CAC07686670C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,16 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EE9FCA-D10E-4AD3-B7B7-5E2676E0473B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36C7EF-D61D-4BC5-9265-3EB5EED0C147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Funil_2" sheetId="2" r:id="rId2"/>
     <sheet name="Funil_3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Funil_2!$A$1:$L$726</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5563,6 +5579,16 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">

--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36C7EF-D61D-4BC5-9265-3EB5EED0C147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCA7E1E-EE4C-4506-95CF-452DFF7E9EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="175">
   <si>
     <t>Data</t>
   </si>
@@ -934,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2212,7 +2212,7 @@
       <c r="P18" s="3">
         <v>7.0601851851851847E-4</v>
       </c>
-      <c r="Q18" s="5">
+      <c r="Q18" s="4">
         <v>1.0500000000000001E-2</v>
       </c>
       <c r="R18" s="4">
@@ -2709,7 +2709,7 @@
       <c r="P25" s="3">
         <v>1.4120370370370369E-3</v>
       </c>
-      <c r="Q25" s="5">
+      <c r="Q25" s="4">
         <v>1.8700000000000001E-2</v>
       </c>
       <c r="R25" s="4">
@@ -4200,7 +4200,7 @@
       <c r="P46" s="3">
         <v>9.9537037037037042E-4</v>
       </c>
-      <c r="Q46" s="5">
+      <c r="Q46" s="4">
         <v>1.6E-2</v>
       </c>
       <c r="R46" s="4">
@@ -4691,25 +4691,25 @@
       <c r="N53">
         <v>0</v>
       </c>
-      <c r="O53" s="3" t="s">
+      <c r="O53" t="s">
         <v>24</v>
       </c>
-      <c r="P53" s="3" t="s">
+      <c r="P53" t="s">
         <v>24</v>
       </c>
-      <c r="Q53" s="4">
-        <v>0</v>
-      </c>
-      <c r="R53" s="4" t="s">
+      <c r="Q53" s="5">
+        <v>0</v>
+      </c>
+      <c r="R53" t="s">
         <v>25</v>
       </c>
-      <c r="S53" s="5" t="s">
+      <c r="S53" t="s">
         <v>25</v>
       </c>
       <c r="T53">
         <v>0</v>
       </c>
-      <c r="U53" s="5" t="s">
+      <c r="U53" t="s">
         <v>25</v>
       </c>
       <c r="V53" s="4">
@@ -4765,7 +4765,7 @@
       <c r="P54" s="3">
         <v>7.5231481481481482E-4</v>
       </c>
-      <c r="Q54" s="5">
+      <c r="Q54" s="4">
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="R54" s="4">
@@ -4913,7 +4913,7 @@
       <c r="R56" s="4">
         <v>4.8599999999999997E-2</v>
       </c>
-      <c r="S56" s="5">
+      <c r="S56" s="4">
         <v>7.4099999999999999E-2</v>
       </c>
       <c r="T56">
@@ -5566,6 +5566,2952 @@
       </c>
       <c r="W65">
         <v>49.881</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B66">
+        <v>8</v>
+      </c>
+      <c r="C66">
+        <v>1018</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66">
+        <v>150800</v>
+      </c>
+      <c r="G66">
+        <v>30</v>
+      </c>
+      <c r="H66">
+        <v>4</v>
+      </c>
+      <c r="I66">
+        <v>45607</v>
+      </c>
+      <c r="J66">
+        <v>675</v>
+      </c>
+      <c r="K66">
+        <v>36</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>34</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="P66" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="R66" s="4">
+        <v>5.33E-2</v>
+      </c>
+      <c r="S66" s="5">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>2</v>
+      </c>
+      <c r="U66" s="4">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="W66">
+        <v>93.465000000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B67">
+        <v>9</v>
+      </c>
+      <c r="C67">
+        <v>1018</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67">
+        <v>150800</v>
+      </c>
+      <c r="G67">
+        <v>30</v>
+      </c>
+      <c r="H67">
+        <v>5</v>
+      </c>
+      <c r="I67">
+        <v>45653</v>
+      </c>
+      <c r="J67">
+        <v>602</v>
+      </c>
+      <c r="K67">
+        <v>38</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>31</v>
+      </c>
+      <c r="N67">
+        <v>2</v>
+      </c>
+      <c r="O67" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P67" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="Q67" s="4">
+        <v>1.32E-2</v>
+      </c>
+      <c r="R67" s="4">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="S67" s="5">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>7</v>
+      </c>
+      <c r="U67" s="4">
+        <v>0.1842</v>
+      </c>
+      <c r="W67">
+        <v>86.039000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B68">
+        <v>10</v>
+      </c>
+      <c r="C68">
+        <v>1018</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>23</v>
+      </c>
+      <c r="F68">
+        <v>150800</v>
+      </c>
+      <c r="G68">
+        <v>30</v>
+      </c>
+      <c r="H68">
+        <v>6</v>
+      </c>
+      <c r="I68">
+        <v>37104</v>
+      </c>
+      <c r="J68">
+        <v>726</v>
+      </c>
+      <c r="K68">
+        <v>32</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>31</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>5.0925925925925921E-4</v>
+      </c>
+      <c r="P68" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="Q68" s="4">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="R68" s="4">
+        <v>4.41E-2</v>
+      </c>
+      <c r="S68" s="5">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68" s="4">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="W68">
+        <v>66.697999999999993</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B69">
+        <v>11</v>
+      </c>
+      <c r="C69">
+        <v>1018</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69">
+        <v>150800</v>
+      </c>
+      <c r="G69">
+        <v>30</v>
+      </c>
+      <c r="H69">
+        <v>4</v>
+      </c>
+      <c r="I69">
+        <v>24703</v>
+      </c>
+      <c r="J69">
+        <v>372</v>
+      </c>
+      <c r="K69">
+        <v>17</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>16</v>
+      </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="P69" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q69" s="4">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="R69" s="4">
+        <v>4.5699999999999998E-2</v>
+      </c>
+      <c r="S69" s="5">
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <v>1</v>
+      </c>
+      <c r="U69" s="4">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="W69">
+        <v>34.572000000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B70">
+        <v>12</v>
+      </c>
+      <c r="C70">
+        <v>1018</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70">
+        <v>150800</v>
+      </c>
+      <c r="G70">
+        <v>30</v>
+      </c>
+      <c r="H70">
+        <v>6</v>
+      </c>
+      <c r="I70">
+        <v>40947</v>
+      </c>
+      <c r="J70">
+        <v>587</v>
+      </c>
+      <c r="K70">
+        <v>34</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>31</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="P70" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="Q70" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="R70" s="4">
+        <v>5.79E-2</v>
+      </c>
+      <c r="S70" s="5">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>3</v>
+      </c>
+      <c r="U70" s="4">
+        <v>8.8200000000000001E-2</v>
+      </c>
+      <c r="W70">
+        <v>64.518000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B71">
+        <v>13</v>
+      </c>
+      <c r="C71">
+        <v>1018</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F71">
+        <v>150800</v>
+      </c>
+      <c r="G71">
+        <v>30</v>
+      </c>
+      <c r="H71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>38080</v>
+      </c>
+      <c r="J71">
+        <v>776</v>
+      </c>
+      <c r="K71">
+        <v>35</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>32</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P71" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="Q71" s="4">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="R71" s="4">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="S71" s="5">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>3</v>
+      </c>
+      <c r="U71" s="4">
+        <v>8.5699999999999998E-2</v>
+      </c>
+      <c r="W71">
+        <v>81.346999999999994</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B72">
+        <v>14</v>
+      </c>
+      <c r="C72">
+        <v>1018</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72">
+        <v>150800</v>
+      </c>
+      <c r="G72">
+        <v>30</v>
+      </c>
+      <c r="H72">
+        <v>6</v>
+      </c>
+      <c r="I72">
+        <v>40724</v>
+      </c>
+      <c r="J72">
+        <v>790</v>
+      </c>
+      <c r="K72">
+        <v>51</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>45</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="P72" s="3">
+        <v>5.6712962962962967E-4</v>
+      </c>
+      <c r="Q72" s="4">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="R72" s="4">
+        <v>6.4600000000000005E-2</v>
+      </c>
+      <c r="S72" s="5">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>6</v>
+      </c>
+      <c r="U72" s="4">
+        <v>0.1176</v>
+      </c>
+      <c r="W72">
+        <v>78.177999999999997</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B73">
+        <v>15</v>
+      </c>
+      <c r="C73">
+        <v>1018</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73">
+        <v>150800</v>
+      </c>
+      <c r="G73">
+        <v>30</v>
+      </c>
+      <c r="H73">
+        <v>6</v>
+      </c>
+      <c r="I73">
+        <v>62644</v>
+      </c>
+      <c r="J73">
+        <v>1167</v>
+      </c>
+      <c r="K73">
+        <v>48</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>45</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="P73" s="3">
+        <v>3.3564814814814812E-4</v>
+      </c>
+      <c r="Q73" s="4">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="R73" s="4">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="S73" s="5">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>3</v>
+      </c>
+      <c r="U73" s="4">
+        <v>6.25E-2</v>
+      </c>
+      <c r="W73">
+        <v>124.74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B74">
+        <v>16</v>
+      </c>
+      <c r="C74">
+        <v>1018</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74">
+        <v>150800</v>
+      </c>
+      <c r="G74">
+        <v>30</v>
+      </c>
+      <c r="H74">
+        <v>4</v>
+      </c>
+      <c r="I74">
+        <v>31388</v>
+      </c>
+      <c r="J74">
+        <v>841</v>
+      </c>
+      <c r="K74">
+        <v>41</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>15</v>
+      </c>
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P74" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="Q74" s="4">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="R74" s="4">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="S74" s="5">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>26</v>
+      </c>
+      <c r="U74" s="4">
+        <v>0.6341</v>
+      </c>
+      <c r="W74">
+        <v>90.176000000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B75">
+        <v>17</v>
+      </c>
+      <c r="C75">
+        <v>1018</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75">
+        <v>150800</v>
+      </c>
+      <c r="G75">
+        <v>30</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>47887</v>
+      </c>
+      <c r="J75">
+        <v>1282</v>
+      </c>
+      <c r="K75">
+        <v>25</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>10</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="P75" s="3">
+        <v>1.0300925925925926E-3</v>
+      </c>
+      <c r="Q75" s="4">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="R75" s="4">
+        <v>1.95E-2</v>
+      </c>
+      <c r="S75" s="5">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>15</v>
+      </c>
+      <c r="U75" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="W75">
+        <v>130.649</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>46189</v>
+      </c>
+      <c r="B76">
+        <v>18</v>
+      </c>
+      <c r="C76">
+        <v>1018</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76">
+        <v>150800</v>
+      </c>
+      <c r="G76">
+        <v>8</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>101</v>
+      </c>
+      <c r="J76">
+        <v>8</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="P76" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q76" s="4">
+        <v>7.9200000000000007E-2</v>
+      </c>
+      <c r="R76" s="5">
+        <v>0</v>
+      </c>
+      <c r="S76" t="s">
+        <v>25</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76" t="s">
+        <v>25</v>
+      </c>
+      <c r="W76">
+        <v>0.16700000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B77">
+        <v>8</v>
+      </c>
+      <c r="C77">
+        <v>1018</v>
+      </c>
+      <c r="D77">
+        <v>1031</v>
+      </c>
+      <c r="E77" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77">
+        <v>206953</v>
+      </c>
+      <c r="G77">
+        <v>30</v>
+      </c>
+      <c r="H77">
+        <v>4</v>
+      </c>
+      <c r="I77">
+        <v>60085</v>
+      </c>
+      <c r="J77">
+        <v>879</v>
+      </c>
+      <c r="K77">
+        <v>32</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>31</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="P77" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="Q77" s="4">
+        <v>1.46E-2</v>
+      </c>
+      <c r="R77" s="4">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="S77" s="5">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+      <c r="U77" s="4">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="V77" s="4">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="W77">
+        <v>111.76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B78">
+        <v>9</v>
+      </c>
+      <c r="C78">
+        <v>1018</v>
+      </c>
+      <c r="D78">
+        <v>1031</v>
+      </c>
+      <c r="E78" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78">
+        <v>206953</v>
+      </c>
+      <c r="G78">
+        <v>30</v>
+      </c>
+      <c r="H78">
+        <v>5</v>
+      </c>
+      <c r="I78">
+        <v>44138</v>
+      </c>
+      <c r="J78">
+        <v>547</v>
+      </c>
+      <c r="K78">
+        <v>30</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>30</v>
+      </c>
+      <c r="N78">
+        <v>2</v>
+      </c>
+      <c r="O78" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="P78" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>1.24E-2</v>
+      </c>
+      <c r="R78" s="4">
+        <v>5.4800000000000001E-2</v>
+      </c>
+      <c r="S78" s="5">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78" s="5">
+        <v>0</v>
+      </c>
+      <c r="V78" s="4">
+        <v>1</v>
+      </c>
+      <c r="W78">
+        <v>76.504999999999995</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B79">
+        <v>10</v>
+      </c>
+      <c r="C79">
+        <v>1018</v>
+      </c>
+      <c r="D79">
+        <v>1031</v>
+      </c>
+      <c r="E79" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79">
+        <v>206953</v>
+      </c>
+      <c r="G79">
+        <v>30</v>
+      </c>
+      <c r="H79">
+        <v>5</v>
+      </c>
+      <c r="I79">
+        <v>49907</v>
+      </c>
+      <c r="J79">
+        <v>629</v>
+      </c>
+      <c r="K79">
+        <v>31</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>27</v>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="P79" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="Q79" s="4">
+        <v>1.26E-2</v>
+      </c>
+      <c r="R79" s="4">
+        <v>4.9299999999999997E-2</v>
+      </c>
+      <c r="S79" s="5">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>4</v>
+      </c>
+      <c r="U79" s="4">
+        <v>0.129</v>
+      </c>
+      <c r="V79" s="4">
+        <v>0.9032</v>
+      </c>
+      <c r="W79">
+        <v>69.36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B80">
+        <v>11</v>
+      </c>
+      <c r="C80">
+        <v>1018</v>
+      </c>
+      <c r="D80">
+        <v>1031</v>
+      </c>
+      <c r="E80" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80">
+        <v>206953</v>
+      </c>
+      <c r="G80">
+        <v>30</v>
+      </c>
+      <c r="H80">
+        <v>5</v>
+      </c>
+      <c r="I80">
+        <v>29903</v>
+      </c>
+      <c r="J80">
+        <v>494</v>
+      </c>
+      <c r="K80">
+        <v>18</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>17</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="P80" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="R80" s="4">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="S80" s="5">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="U80" s="4">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="V80" s="4">
+        <v>0.95</v>
+      </c>
+      <c r="W80">
+        <v>44.927999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B81">
+        <v>12</v>
+      </c>
+      <c r="C81">
+        <v>1018</v>
+      </c>
+      <c r="D81">
+        <v>1031</v>
+      </c>
+      <c r="E81" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81">
+        <v>206953</v>
+      </c>
+      <c r="G81">
+        <v>30</v>
+      </c>
+      <c r="H81">
+        <v>3</v>
+      </c>
+      <c r="I81">
+        <v>13260</v>
+      </c>
+      <c r="J81">
+        <v>201</v>
+      </c>
+      <c r="K81">
+        <v>11</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>9</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="P81" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q81" s="4">
+        <v>1.52E-2</v>
+      </c>
+      <c r="R81" s="4">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="S81" s="5">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>2</v>
+      </c>
+      <c r="U81" s="4">
+        <v>0.18179999999999999</v>
+      </c>
+      <c r="V81" s="4">
+        <v>0.91669999999999996</v>
+      </c>
+      <c r="W81">
+        <v>18.963000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B82">
+        <v>13</v>
+      </c>
+      <c r="C82">
+        <v>1018</v>
+      </c>
+      <c r="D82">
+        <v>1031</v>
+      </c>
+      <c r="E82" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82">
+        <v>206953</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>292</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82" s="3">
+        <v>1.4583333333333334E-3</v>
+      </c>
+      <c r="P82" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q82" s="4">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="R82" s="5">
+        <v>0</v>
+      </c>
+      <c r="S82" t="s">
+        <v>25</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82" t="s">
+        <v>25</v>
+      </c>
+      <c r="V82" t="s">
+        <v>25</v>
+      </c>
+      <c r="W82">
+        <v>0.28699999999999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B83">
+        <v>14</v>
+      </c>
+      <c r="C83">
+        <v>1018</v>
+      </c>
+      <c r="D83">
+        <v>1031</v>
+      </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83">
+        <v>206953</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>80</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83" t="s">
+        <v>24</v>
+      </c>
+      <c r="P83" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q83" s="5">
+        <v>0</v>
+      </c>
+      <c r="R83" t="s">
+        <v>25</v>
+      </c>
+      <c r="S83" t="s">
+        <v>25</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83" t="s">
+        <v>25</v>
+      </c>
+      <c r="V83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B84">
+        <v>15</v>
+      </c>
+      <c r="C84">
+        <v>1018</v>
+      </c>
+      <c r="D84">
+        <v>1031</v>
+      </c>
+      <c r="E84" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84">
+        <v>206953</v>
+      </c>
+      <c r="G84">
+        <v>30</v>
+      </c>
+      <c r="H84">
+        <v>5</v>
+      </c>
+      <c r="I84">
+        <v>33949</v>
+      </c>
+      <c r="J84">
+        <v>369</v>
+      </c>
+      <c r="K84">
+        <v>10</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>10</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="P84" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+      <c r="Q84" s="4">
+        <v>1.09E-2</v>
+      </c>
+      <c r="R84" s="4">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="S84" s="5">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84" s="5">
+        <v>0</v>
+      </c>
+      <c r="V84" s="4">
+        <v>1</v>
+      </c>
+      <c r="W84">
+        <v>58.966999999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B85">
+        <v>16</v>
+      </c>
+      <c r="C85">
+        <v>1018</v>
+      </c>
+      <c r="D85">
+        <v>1031</v>
+      </c>
+      <c r="E85" t="s">
+        <v>23</v>
+      </c>
+      <c r="F85">
+        <v>206953</v>
+      </c>
+      <c r="G85">
+        <v>30</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+      <c r="I85">
+        <v>31353</v>
+      </c>
+      <c r="J85">
+        <v>443</v>
+      </c>
+      <c r="K85">
+        <v>17</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>13</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="P85" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>1.41E-2</v>
+      </c>
+      <c r="R85" s="4">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="S85" s="5">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>4</v>
+      </c>
+      <c r="U85" s="4">
+        <v>0.23530000000000001</v>
+      </c>
+      <c r="V85" s="4">
+        <v>0.8125</v>
+      </c>
+      <c r="W85">
+        <v>60.308999999999997</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B86">
+        <v>17</v>
+      </c>
+      <c r="C86">
+        <v>1018</v>
+      </c>
+      <c r="D86">
+        <v>1031</v>
+      </c>
+      <c r="E86" t="s">
+        <v>23</v>
+      </c>
+      <c r="F86">
+        <v>206953</v>
+      </c>
+      <c r="G86">
+        <v>30</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+      <c r="I86">
+        <v>19594</v>
+      </c>
+      <c r="J86">
+        <v>362</v>
+      </c>
+      <c r="K86">
+        <v>15</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>14</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="P86" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+      <c r="Q86" s="4">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="R86" s="4">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="S86" s="5">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>1</v>
+      </c>
+      <c r="U86" s="4">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="V86" s="4">
+        <v>0.9375</v>
+      </c>
+      <c r="W86">
+        <v>32.674999999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B87">
+        <v>8</v>
+      </c>
+      <c r="C87">
+        <v>1018</v>
+      </c>
+      <c r="D87">
+        <v>1031</v>
+      </c>
+      <c r="E87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87">
+        <v>160040</v>
+      </c>
+      <c r="G87">
+        <v>30</v>
+      </c>
+      <c r="H87">
+        <v>5</v>
+      </c>
+      <c r="I87">
+        <v>50983</v>
+      </c>
+      <c r="J87">
+        <v>649</v>
+      </c>
+      <c r="K87">
+        <v>20</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>20</v>
+      </c>
+      <c r="N87">
+        <v>3</v>
+      </c>
+      <c r="O87" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P87" s="3">
+        <v>9.7222222222222219E-4</v>
+      </c>
+      <c r="Q87" s="4">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="R87" s="4">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="S87" s="5">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>0</v>
+      </c>
+      <c r="U87" s="5">
+        <v>0</v>
+      </c>
+      <c r="V87" s="4">
+        <v>1</v>
+      </c>
+      <c r="W87">
+        <v>76.528000000000006</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B88">
+        <v>9</v>
+      </c>
+      <c r="C88">
+        <v>1018</v>
+      </c>
+      <c r="D88">
+        <v>1031</v>
+      </c>
+      <c r="E88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88">
+        <v>160040</v>
+      </c>
+      <c r="G88">
+        <v>30</v>
+      </c>
+      <c r="H88">
+        <v>5</v>
+      </c>
+      <c r="I88">
+        <v>34125</v>
+      </c>
+      <c r="J88">
+        <v>386</v>
+      </c>
+      <c r="K88">
+        <v>16</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>13</v>
+      </c>
+      <c r="N88">
+        <v>1</v>
+      </c>
+      <c r="O88" s="3">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="P88" s="3">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="Q88" s="4">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="R88" s="4">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="S88" s="5">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>3</v>
+      </c>
+      <c r="U88" s="4">
+        <v>0.1875</v>
+      </c>
+      <c r="V88" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="W88">
+        <v>59.408000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B89">
+        <v>10</v>
+      </c>
+      <c r="C89">
+        <v>1018</v>
+      </c>
+      <c r="D89">
+        <v>1031</v>
+      </c>
+      <c r="E89" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89">
+        <v>160040</v>
+      </c>
+      <c r="G89">
+        <v>30</v>
+      </c>
+      <c r="H89">
+        <v>5</v>
+      </c>
+      <c r="I89">
+        <v>22976</v>
+      </c>
+      <c r="J89">
+        <v>257</v>
+      </c>
+      <c r="K89">
+        <v>8</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>8</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="P89" s="3">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="Q89" s="4">
+        <v>1.12E-2</v>
+      </c>
+      <c r="R89" s="4">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="S89" s="5">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89" s="5">
+        <v>0</v>
+      </c>
+      <c r="V89" s="4">
+        <v>1</v>
+      </c>
+      <c r="W89">
+        <v>37.344000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B90">
+        <v>11</v>
+      </c>
+      <c r="C90">
+        <v>1018</v>
+      </c>
+      <c r="D90">
+        <v>1031</v>
+      </c>
+      <c r="E90" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90">
+        <v>160040</v>
+      </c>
+      <c r="G90">
+        <v>30</v>
+      </c>
+      <c r="H90">
+        <v>7</v>
+      </c>
+      <c r="I90">
+        <v>46618</v>
+      </c>
+      <c r="J90">
+        <v>867</v>
+      </c>
+      <c r="K90">
+        <v>43</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>42</v>
+      </c>
+      <c r="N90">
+        <v>2</v>
+      </c>
+      <c r="O90" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="P90" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="Q90" s="4">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="R90" s="4">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="S90" s="5">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>1</v>
+      </c>
+      <c r="U90" s="4">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="V90" s="4">
+        <v>0.97670000000000001</v>
+      </c>
+      <c r="W90">
+        <v>94.141000000000005</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B91">
+        <v>12</v>
+      </c>
+      <c r="C91">
+        <v>1018</v>
+      </c>
+      <c r="D91">
+        <v>1031</v>
+      </c>
+      <c r="E91" t="s">
+        <v>23</v>
+      </c>
+      <c r="F91">
+        <v>160040</v>
+      </c>
+      <c r="G91">
+        <v>30</v>
+      </c>
+      <c r="H91">
+        <v>6</v>
+      </c>
+      <c r="I91">
+        <v>37549</v>
+      </c>
+      <c r="J91">
+        <v>807</v>
+      </c>
+      <c r="K91">
+        <v>40</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>38</v>
+      </c>
+      <c r="N91">
+        <v>2</v>
+      </c>
+      <c r="O91" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="P91" s="3">
+        <v>8.1018518518518516E-4</v>
+      </c>
+      <c r="Q91" s="4">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="R91" s="4">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="S91" s="5">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>2</v>
+      </c>
+      <c r="U91" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="V91" s="4">
+        <v>0.92110000000000003</v>
+      </c>
+      <c r="W91">
+        <v>88.382999999999996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B92">
+        <v>13</v>
+      </c>
+      <c r="C92">
+        <v>1018</v>
+      </c>
+      <c r="D92">
+        <v>1031</v>
+      </c>
+      <c r="E92" t="s">
+        <v>23</v>
+      </c>
+      <c r="F92">
+        <v>160040</v>
+      </c>
+      <c r="G92">
+        <v>30</v>
+      </c>
+      <c r="H92">
+        <v>2</v>
+      </c>
+      <c r="I92">
+        <v>8571</v>
+      </c>
+      <c r="J92">
+        <v>164</v>
+      </c>
+      <c r="K92">
+        <v>3</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>2</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="P92" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="Q92" s="4">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="R92" s="4">
+        <v>1.83E-2</v>
+      </c>
+      <c r="S92" s="5">
+        <v>0</v>
+      </c>
+      <c r="T92">
+        <v>1</v>
+      </c>
+      <c r="U92" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V92" s="4">
+        <v>1</v>
+      </c>
+      <c r="W92">
+        <v>19.939</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B93">
+        <v>14</v>
+      </c>
+      <c r="C93">
+        <v>1018</v>
+      </c>
+      <c r="D93">
+        <v>1031</v>
+      </c>
+      <c r="E93" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93">
+        <v>160040</v>
+      </c>
+      <c r="G93">
+        <v>30</v>
+      </c>
+      <c r="H93">
+        <v>6</v>
+      </c>
+      <c r="I93">
+        <v>27244</v>
+      </c>
+      <c r="J93">
+        <v>627</v>
+      </c>
+      <c r="K93">
+        <v>28</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>26</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
+      <c r="O93" s="3">
+        <v>4.7453703703703704E-4</v>
+      </c>
+      <c r="P93" s="3">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="Q93" s="4">
+        <v>2.3E-2</v>
+      </c>
+      <c r="R93" s="4">
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="S93" s="5">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>2</v>
+      </c>
+      <c r="U93" s="4">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="V93" s="4">
+        <v>1</v>
+      </c>
+      <c r="W93">
+        <v>67.114999999999995</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B94">
+        <v>15</v>
+      </c>
+      <c r="C94">
+        <v>1018</v>
+      </c>
+      <c r="D94">
+        <v>1031</v>
+      </c>
+      <c r="E94" t="s">
+        <v>23</v>
+      </c>
+      <c r="F94">
+        <v>160040</v>
+      </c>
+      <c r="G94">
+        <v>30</v>
+      </c>
+      <c r="H94">
+        <v>6</v>
+      </c>
+      <c r="I94">
+        <v>43463</v>
+      </c>
+      <c r="J94">
+        <v>738</v>
+      </c>
+      <c r="K94">
+        <v>32</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>32</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="P94" s="3">
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="Q94" s="4">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="R94" s="4">
+        <v>4.3400000000000001E-2</v>
+      </c>
+      <c r="S94" s="5">
+        <v>0</v>
+      </c>
+      <c r="T94">
+        <v>0</v>
+      </c>
+      <c r="U94" s="5">
+        <v>0</v>
+      </c>
+      <c r="V94" s="4">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="W94">
+        <v>113.578</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B95">
+        <v>16</v>
+      </c>
+      <c r="C95">
+        <v>1018</v>
+      </c>
+      <c r="D95">
+        <v>1031</v>
+      </c>
+      <c r="E95" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95">
+        <v>160040</v>
+      </c>
+      <c r="G95">
+        <v>23</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>15968</v>
+      </c>
+      <c r="J95">
+        <v>28</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3">
+        <v>5.9722222222222225E-3</v>
+      </c>
+      <c r="P95" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q95" s="4">
+        <v>1.8E-3</v>
+      </c>
+      <c r="R95" s="5">
+        <v>0</v>
+      </c>
+      <c r="S95" t="s">
+        <v>25</v>
+      </c>
+      <c r="T95">
+        <v>0</v>
+      </c>
+      <c r="U95" t="s">
+        <v>25</v>
+      </c>
+      <c r="V95" s="4">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="W95">
+        <v>39.295000000000002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B96">
+        <v>17</v>
+      </c>
+      <c r="C96">
+        <v>1018</v>
+      </c>
+      <c r="D96">
+        <v>1031</v>
+      </c>
+      <c r="E96" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96">
+        <v>160040</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>24318</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96" t="s">
+        <v>24</v>
+      </c>
+      <c r="P96" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>0</v>
+      </c>
+      <c r="R96" t="s">
+        <v>25</v>
+      </c>
+      <c r="S96" t="s">
+        <v>25</v>
+      </c>
+      <c r="T96">
+        <v>0</v>
+      </c>
+      <c r="U96" t="s">
+        <v>25</v>
+      </c>
+      <c r="V96" s="4">
+        <v>0.8286</v>
+      </c>
+      <c r="W96">
+        <v>74.239000000000004</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B97">
+        <v>18</v>
+      </c>
+      <c r="C97">
+        <v>1018</v>
+      </c>
+      <c r="D97">
+        <v>1031</v>
+      </c>
+      <c r="E97" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97">
+        <v>160040</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>7</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>24</v>
+      </c>
+      <c r="P97" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q97" s="5">
+        <v>0</v>
+      </c>
+      <c r="R97" t="s">
+        <v>25</v>
+      </c>
+      <c r="S97" t="s">
+        <v>25</v>
+      </c>
+      <c r="T97">
+        <v>0</v>
+      </c>
+      <c r="U97" t="s">
+        <v>25</v>
+      </c>
+      <c r="V97" t="s">
+        <v>25</v>
+      </c>
+      <c r="W97">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B98">
+        <v>8</v>
+      </c>
+      <c r="C98">
+        <v>1018</v>
+      </c>
+      <c r="D98">
+        <v>1031</v>
+      </c>
+      <c r="E98" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98">
+        <v>256708</v>
+      </c>
+      <c r="G98">
+        <v>30</v>
+      </c>
+      <c r="H98">
+        <v>7</v>
+      </c>
+      <c r="I98">
+        <v>43920</v>
+      </c>
+      <c r="J98">
+        <v>475</v>
+      </c>
+      <c r="K98">
+        <v>24</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>24</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" s="3">
+        <v>8.4490740740740739E-4</v>
+      </c>
+      <c r="P98" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="Q98" s="4">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="R98" s="4">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="S98" s="5">
+        <v>0</v>
+      </c>
+      <c r="T98">
+        <v>0</v>
+      </c>
+      <c r="U98" s="5">
+        <v>0</v>
+      </c>
+      <c r="V98" s="4">
+        <v>0.95650000000000002</v>
+      </c>
+      <c r="W98">
+        <v>83.201999999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B99">
+        <v>9</v>
+      </c>
+      <c r="C99">
+        <v>1018</v>
+      </c>
+      <c r="D99">
+        <v>1031</v>
+      </c>
+      <c r="E99" t="s">
+        <v>23</v>
+      </c>
+      <c r="F99">
+        <v>256708</v>
+      </c>
+      <c r="G99">
+        <v>30</v>
+      </c>
+      <c r="H99">
+        <v>6</v>
+      </c>
+      <c r="I99">
+        <v>53708</v>
+      </c>
+      <c r="J99">
+        <v>408</v>
+      </c>
+      <c r="K99">
+        <v>22</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>22</v>
+      </c>
+      <c r="N99">
+        <v>2</v>
+      </c>
+      <c r="O99" s="3">
+        <v>1.2037037037037038E-3</v>
+      </c>
+      <c r="P99" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="Q99" s="4">
+        <v>7.6E-3</v>
+      </c>
+      <c r="R99" s="4">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="S99" s="5">
+        <v>0</v>
+      </c>
+      <c r="T99">
+        <v>0</v>
+      </c>
+      <c r="U99" s="5">
+        <v>0</v>
+      </c>
+      <c r="V99" s="4">
+        <v>1</v>
+      </c>
+      <c r="W99">
+        <v>98.563000000000002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B100">
+        <v>10</v>
+      </c>
+      <c r="C100">
+        <v>1018</v>
+      </c>
+      <c r="D100">
+        <v>1031</v>
+      </c>
+      <c r="E100" t="s">
+        <v>23</v>
+      </c>
+      <c r="F100">
+        <v>256708</v>
+      </c>
+      <c r="G100">
+        <v>30</v>
+      </c>
+      <c r="H100">
+        <v>8</v>
+      </c>
+      <c r="I100">
+        <v>45462</v>
+      </c>
+      <c r="J100">
+        <v>318</v>
+      </c>
+      <c r="K100">
+        <v>18</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>18</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100" s="3">
+        <v>1.3657407407407407E-3</v>
+      </c>
+      <c r="P100" s="3">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="Q100" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R100" s="4">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="S100" s="5">
+        <v>0</v>
+      </c>
+      <c r="T100">
+        <v>0</v>
+      </c>
+      <c r="U100" s="5">
+        <v>0</v>
+      </c>
+      <c r="V100" s="4">
+        <v>1</v>
+      </c>
+      <c r="W100">
+        <v>89.965999999999994</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B101">
+        <v>11</v>
+      </c>
+      <c r="C101">
+        <v>1018</v>
+      </c>
+      <c r="D101">
+        <v>1031</v>
+      </c>
+      <c r="E101" t="s">
+        <v>23</v>
+      </c>
+      <c r="F101">
+        <v>256708</v>
+      </c>
+      <c r="G101">
+        <v>30</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+      <c r="I101">
+        <v>40160</v>
+      </c>
+      <c r="J101">
+        <v>302</v>
+      </c>
+      <c r="K101">
+        <v>15</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>14</v>
+      </c>
+      <c r="N101">
+        <v>4</v>
+      </c>
+      <c r="O101" s="3">
+        <v>1.238425925925926E-3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>1.6898148148148148E-3</v>
+      </c>
+      <c r="Q101" s="4">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="R101" s="4">
+        <v>4.9700000000000001E-2</v>
+      </c>
+      <c r="S101" s="5">
+        <v>0</v>
+      </c>
+      <c r="T101">
+        <v>1</v>
+      </c>
+      <c r="U101" s="4">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="V101" s="4">
+        <v>0.69230000000000003</v>
+      </c>
+      <c r="W101">
+        <v>83.59</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B102">
+        <v>12</v>
+      </c>
+      <c r="C102">
+        <v>1018</v>
+      </c>
+      <c r="D102">
+        <v>1031</v>
+      </c>
+      <c r="E102" t="s">
+        <v>23</v>
+      </c>
+      <c r="F102">
+        <v>256708</v>
+      </c>
+      <c r="G102">
+        <v>30</v>
+      </c>
+      <c r="H102">
+        <v>4</v>
+      </c>
+      <c r="I102">
+        <v>46250</v>
+      </c>
+      <c r="J102">
+        <v>259</v>
+      </c>
+      <c r="K102">
+        <v>17</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>14</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>1.6898148148148148E-3</v>
+      </c>
+      <c r="P102" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="Q102" s="4">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="R102" s="4">
+        <v>6.5600000000000006E-2</v>
+      </c>
+      <c r="S102" s="5">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>3</v>
+      </c>
+      <c r="U102" s="4">
+        <v>0.17649999999999999</v>
+      </c>
+      <c r="V102" s="4">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="W102">
+        <v>102.41800000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B103">
+        <v>13</v>
+      </c>
+      <c r="C103">
+        <v>1018</v>
+      </c>
+      <c r="D103">
+        <v>1031</v>
+      </c>
+      <c r="E103" t="s">
+        <v>23</v>
+      </c>
+      <c r="F103">
+        <v>256708</v>
+      </c>
+      <c r="G103">
+        <v>30</v>
+      </c>
+      <c r="H103">
+        <v>2</v>
+      </c>
+      <c r="I103">
+        <v>44096</v>
+      </c>
+      <c r="J103">
+        <v>313</v>
+      </c>
+      <c r="K103">
+        <v>14</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>12</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" s="3">
+        <v>1.2847222222222223E-3</v>
+      </c>
+      <c r="P103" s="3">
+        <v>1.1111111111111111E-3</v>
+      </c>
+      <c r="Q103" s="4">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R103" s="4">
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="S103" s="5">
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <v>2</v>
+      </c>
+      <c r="U103" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="V103" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="W103">
+        <v>102.626</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B104">
+        <v>14</v>
+      </c>
+      <c r="C104">
+        <v>1018</v>
+      </c>
+      <c r="D104">
+        <v>1031</v>
+      </c>
+      <c r="E104" t="s">
+        <v>23</v>
+      </c>
+      <c r="F104">
+        <v>256708</v>
+      </c>
+      <c r="G104">
+        <v>30</v>
+      </c>
+      <c r="H104">
+        <v>6</v>
+      </c>
+      <c r="I104">
+        <v>44661</v>
+      </c>
+      <c r="J104">
+        <v>530</v>
+      </c>
+      <c r="K104">
+        <v>28</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>24</v>
+      </c>
+      <c r="N104">
+        <v>2</v>
+      </c>
+      <c r="O104" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="P104" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="Q104" s="4">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="R104" s="4">
+        <v>5.28E-2</v>
+      </c>
+      <c r="S104" s="5">
+        <v>0</v>
+      </c>
+      <c r="T104">
+        <v>4</v>
+      </c>
+      <c r="U104" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="V104" s="4">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="W104">
+        <v>108.878</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B105">
+        <v>15</v>
+      </c>
+      <c r="C105">
+        <v>1018</v>
+      </c>
+      <c r="D105">
+        <v>1031</v>
+      </c>
+      <c r="E105" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105">
+        <v>256708</v>
+      </c>
+      <c r="G105">
+        <v>30</v>
+      </c>
+      <c r="H105">
+        <v>4</v>
+      </c>
+      <c r="I105">
+        <v>46889</v>
+      </c>
+      <c r="J105">
+        <v>538</v>
+      </c>
+      <c r="K105">
+        <v>17</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>16</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105" s="3">
+        <v>8.4490740740740739E-4</v>
+      </c>
+      <c r="P105" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+      <c r="Q105" s="4">
+        <v>1.15E-2</v>
+      </c>
+      <c r="R105" s="4">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="S105" s="5">
+        <v>0</v>
+      </c>
+      <c r="T105">
+        <v>1</v>
+      </c>
+      <c r="U105" s="4">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="V105" s="4">
+        <v>1</v>
+      </c>
+      <c r="W105">
+        <v>107.911</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B106">
+        <v>16</v>
+      </c>
+      <c r="C106">
+        <v>1018</v>
+      </c>
+      <c r="D106">
+        <v>1031</v>
+      </c>
+      <c r="E106" t="s">
+        <v>23</v>
+      </c>
+      <c r="F106">
+        <v>256708</v>
+      </c>
+      <c r="G106">
+        <v>30</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+      <c r="I106">
+        <v>35872</v>
+      </c>
+      <c r="J106">
+        <v>460</v>
+      </c>
+      <c r="K106">
+        <v>18</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>17</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="P106" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="Q106" s="4">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="R106" s="4">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="S106" s="5">
+        <v>0</v>
+      </c>
+      <c r="T106">
+        <v>1</v>
+      </c>
+      <c r="U106" s="4">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="V106" s="4">
+        <v>0.76470000000000005</v>
+      </c>
+      <c r="W106">
+        <v>82.001999999999995</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B107">
+        <v>17</v>
+      </c>
+      <c r="C107">
+        <v>1018</v>
+      </c>
+      <c r="D107">
+        <v>1031</v>
+      </c>
+      <c r="E107" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107">
+        <v>256708</v>
+      </c>
+      <c r="G107">
+        <v>30</v>
+      </c>
+      <c r="H107">
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <v>39302</v>
+      </c>
+      <c r="J107">
+        <v>361</v>
+      </c>
+      <c r="K107">
+        <v>21</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>19</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="P107" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="Q107" s="4">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="R107" s="4">
+        <v>5.8200000000000002E-2</v>
+      </c>
+      <c r="S107" s="5">
+        <v>0</v>
+      </c>
+      <c r="T107">
+        <v>2</v>
+      </c>
+      <c r="U107" s="4">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="V107" s="4">
+        <v>0.88890000000000002</v>
+      </c>
+      <c r="W107">
+        <v>90.763999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/data/base_renac.xlsx
+++ b/data/base_renac.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.15.5.30\Variados\Gerber\Relatório\Github\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCA7E1E-EE4C-4506-95CF-452DFF7E9EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57380137-5321-41BF-B826-3D48155F1679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="175">
   <si>
     <t>Data</t>
   </si>
@@ -934,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W107"/>
+  <dimension ref="A1:W153"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -8514,6 +8514,3272 @@
         <v>90.763999999999996</v>
       </c>
     </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B108">
+        <v>8</v>
+      </c>
+      <c r="C108">
+        <v>1018</v>
+      </c>
+      <c r="D108">
+        <v>1031</v>
+      </c>
+      <c r="E108" t="s">
+        <v>23</v>
+      </c>
+      <c r="F108">
+        <v>105434</v>
+      </c>
+      <c r="G108">
+        <v>10</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>37130</v>
+      </c>
+      <c r="J108">
+        <v>473</v>
+      </c>
+      <c r="K108">
+        <v>22</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>21</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="P108" s="3">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="Q108" s="4">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="R108" s="4">
+        <v>4.65E-2</v>
+      </c>
+      <c r="S108" s="5">
+        <v>0</v>
+      </c>
+      <c r="T108">
+        <v>1</v>
+      </c>
+      <c r="U108" s="4">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="V108" s="4">
+        <v>0.71430000000000005</v>
+      </c>
+      <c r="W108">
+        <v>82.742999999999995</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B109">
+        <v>9</v>
+      </c>
+      <c r="C109">
+        <v>1018</v>
+      </c>
+      <c r="D109">
+        <v>1031</v>
+      </c>
+      <c r="E109" t="s">
+        <v>23</v>
+      </c>
+      <c r="F109">
+        <v>105434</v>
+      </c>
+      <c r="G109">
+        <v>10</v>
+      </c>
+      <c r="H109">
+        <v>3</v>
+      </c>
+      <c r="I109">
+        <v>48204</v>
+      </c>
+      <c r="J109">
+        <v>523</v>
+      </c>
+      <c r="K109">
+        <v>21</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>18</v>
+      </c>
+      <c r="N109">
+        <v>3</v>
+      </c>
+      <c r="O109" s="3">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="P109" s="3">
+        <v>9.2592592592592596E-4</v>
+      </c>
+      <c r="Q109" s="4">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="R109" s="4">
+        <v>4.02E-2</v>
+      </c>
+      <c r="S109" s="5">
+        <v>0</v>
+      </c>
+      <c r="T109">
+        <v>3</v>
+      </c>
+      <c r="U109" s="4">
+        <v>0.1429</v>
+      </c>
+      <c r="V109" s="4">
+        <v>0.82609999999999995</v>
+      </c>
+      <c r="W109">
+        <v>94.932000000000002</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B110">
+        <v>10</v>
+      </c>
+      <c r="C110">
+        <v>1018</v>
+      </c>
+      <c r="D110">
+        <v>1031</v>
+      </c>
+      <c r="E110" t="s">
+        <v>23</v>
+      </c>
+      <c r="F110">
+        <v>105434</v>
+      </c>
+      <c r="G110">
+        <v>10</v>
+      </c>
+      <c r="H110">
+        <v>3</v>
+      </c>
+      <c r="I110">
+        <v>48336</v>
+      </c>
+      <c r="J110">
+        <v>320</v>
+      </c>
+      <c r="K110">
+        <v>17</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>17</v>
+      </c>
+      <c r="N110">
+        <v>2</v>
+      </c>
+      <c r="O110" s="3">
+        <v>1.3541666666666667E-3</v>
+      </c>
+      <c r="P110" s="3">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="Q110" s="4">
+        <v>6.6E-3</v>
+      </c>
+      <c r="R110" s="4">
+        <v>5.3100000000000001E-2</v>
+      </c>
+      <c r="S110" s="5">
+        <v>0</v>
+      </c>
+      <c r="T110">
+        <v>0</v>
+      </c>
+      <c r="U110" s="5">
+        <v>0</v>
+      </c>
+      <c r="V110" s="4">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="W110">
+        <v>53.32</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B111">
+        <v>11</v>
+      </c>
+      <c r="C111">
+        <v>1018</v>
+      </c>
+      <c r="D111">
+        <v>1031</v>
+      </c>
+      <c r="E111" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111">
+        <v>105434</v>
+      </c>
+      <c r="G111">
+        <v>10</v>
+      </c>
+      <c r="H111">
+        <v>4</v>
+      </c>
+      <c r="I111">
+        <v>50335</v>
+      </c>
+      <c r="J111">
+        <v>618</v>
+      </c>
+      <c r="K111">
+        <v>33</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>33</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111" s="3">
+        <v>6.8287037037037036E-4</v>
+      </c>
+      <c r="P111" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="Q111" s="4">
+        <v>1.23E-2</v>
+      </c>
+      <c r="R111" s="4">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="S111" s="5">
+        <v>0</v>
+      </c>
+      <c r="T111">
+        <v>0</v>
+      </c>
+      <c r="U111" s="5">
+        <v>0</v>
+      </c>
+      <c r="V111" s="4">
+        <v>0.90910000000000002</v>
+      </c>
+      <c r="W111">
+        <v>108.577</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B112">
+        <v>12</v>
+      </c>
+      <c r="C112">
+        <v>1018</v>
+      </c>
+      <c r="D112">
+        <v>1031</v>
+      </c>
+      <c r="E112" t="s">
+        <v>23</v>
+      </c>
+      <c r="F112">
+        <v>105434</v>
+      </c>
+      <c r="G112">
+        <v>10</v>
+      </c>
+      <c r="H112">
+        <v>4</v>
+      </c>
+      <c r="I112">
+        <v>72915</v>
+      </c>
+      <c r="J112">
+        <v>869</v>
+      </c>
+      <c r="K112">
+        <v>35</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>34</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="P112" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="Q112" s="4">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="R112" s="4">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="S112" s="5">
+        <v>0</v>
+      </c>
+      <c r="T112">
+        <v>1</v>
+      </c>
+      <c r="U112" s="4">
+        <v>2.86E-2</v>
+      </c>
+      <c r="V112" s="4">
+        <v>0.90629999999999999</v>
+      </c>
+      <c r="W112">
+        <v>126.782</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B113">
+        <v>13</v>
+      </c>
+      <c r="C113">
+        <v>1018</v>
+      </c>
+      <c r="D113">
+        <v>1031</v>
+      </c>
+      <c r="E113" t="s">
+        <v>23</v>
+      </c>
+      <c r="F113">
+        <v>105434</v>
+      </c>
+      <c r="G113">
+        <v>10</v>
+      </c>
+      <c r="H113">
+        <v>4</v>
+      </c>
+      <c r="I113">
+        <v>43156</v>
+      </c>
+      <c r="J113">
+        <v>660</v>
+      </c>
+      <c r="K113">
+        <v>30</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>24</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="P113" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="Q113" s="4">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="R113" s="4">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="S113" s="5">
+        <v>0</v>
+      </c>
+      <c r="T113">
+        <v>6</v>
+      </c>
+      <c r="U113" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="V113" s="4">
+        <v>0.78790000000000004</v>
+      </c>
+      <c r="W113">
+        <v>93.278999999999996</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B114">
+        <v>14</v>
+      </c>
+      <c r="C114">
+        <v>1018</v>
+      </c>
+      <c r="D114">
+        <v>1031</v>
+      </c>
+      <c r="E114" t="s">
+        <v>23</v>
+      </c>
+      <c r="F114">
+        <v>105434</v>
+      </c>
+      <c r="G114">
+        <v>10</v>
+      </c>
+      <c r="H114">
+        <v>3</v>
+      </c>
+      <c r="I114">
+        <v>39847</v>
+      </c>
+      <c r="J114">
+        <v>521</v>
+      </c>
+      <c r="K114">
+        <v>24</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>22</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114" s="3">
+        <v>7.5231481481481482E-4</v>
+      </c>
+      <c r="P114" s="3">
+        <v>3.7037037037037035E-4</v>
+      </c>
+      <c r="Q114" s="4">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="R114" s="4">
+        <v>4.6100000000000002E-2</v>
+      </c>
+      <c r="S114" s="5">
+        <v>0</v>
+      </c>
+      <c r="T114">
+        <v>2</v>
+      </c>
+      <c r="U114" s="4">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="V114" s="4">
+        <v>0.86960000000000004</v>
+      </c>
+      <c r="W114">
+        <v>91.525999999999996</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B115">
+        <v>15</v>
+      </c>
+      <c r="C115">
+        <v>1018</v>
+      </c>
+      <c r="D115">
+        <v>1031</v>
+      </c>
+      <c r="E115" t="s">
+        <v>23</v>
+      </c>
+      <c r="F115">
+        <v>105434</v>
+      </c>
+      <c r="G115">
+        <v>10</v>
+      </c>
+      <c r="H115">
+        <v>3</v>
+      </c>
+      <c r="I115">
+        <v>45299</v>
+      </c>
+      <c r="J115">
+        <v>504</v>
+      </c>
+      <c r="K115">
+        <v>25</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>21</v>
+      </c>
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" s="3">
+        <v>8.6805555555555551E-4</v>
+      </c>
+      <c r="P115" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="Q115" s="4">
+        <v>1.11E-2</v>
+      </c>
+      <c r="R115" s="4">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="S115" s="5">
+        <v>0</v>
+      </c>
+      <c r="T115">
+        <v>4</v>
+      </c>
+      <c r="U115" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="V115" s="4">
+        <v>0.76919999999999999</v>
+      </c>
+      <c r="W115">
+        <v>93.947000000000003</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B116">
+        <v>16</v>
+      </c>
+      <c r="C116">
+        <v>1018</v>
+      </c>
+      <c r="D116">
+        <v>1031</v>
+      </c>
+      <c r="E116" t="s">
+        <v>23</v>
+      </c>
+      <c r="F116">
+        <v>105434</v>
+      </c>
+      <c r="G116">
+        <v>10</v>
+      </c>
+      <c r="H116">
+        <v>2</v>
+      </c>
+      <c r="I116">
+        <v>43100</v>
+      </c>
+      <c r="J116">
+        <v>493</v>
+      </c>
+      <c r="K116">
+        <v>19</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>18</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116" s="3">
+        <v>8.2175925925925927E-4</v>
+      </c>
+      <c r="P116" s="3">
+        <v>5.9027777777777778E-4</v>
+      </c>
+      <c r="Q116" s="4">
+        <v>1.14E-2</v>
+      </c>
+      <c r="R116" s="4">
+        <v>3.85E-2</v>
+      </c>
+      <c r="S116" s="5">
+        <v>0</v>
+      </c>
+      <c r="T116">
+        <v>1</v>
+      </c>
+      <c r="U116" s="4">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="V116" s="4">
+        <v>0.78949999999999998</v>
+      </c>
+      <c r="W116">
+        <v>81.882999999999996</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B117">
+        <v>17</v>
+      </c>
+      <c r="C117">
+        <v>1018</v>
+      </c>
+      <c r="D117">
+        <v>1031</v>
+      </c>
+      <c r="E117" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117">
+        <v>105434</v>
+      </c>
+      <c r="G117">
+        <v>10</v>
+      </c>
+      <c r="H117">
+        <v>2</v>
+      </c>
+      <c r="I117">
+        <v>42987</v>
+      </c>
+      <c r="J117">
+        <v>362</v>
+      </c>
+      <c r="K117">
+        <v>21</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>14</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117" s="3">
+        <v>1.0532407407407407E-3</v>
+      </c>
+      <c r="P117" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q117" s="4">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="R117" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="S117" s="5">
+        <v>0</v>
+      </c>
+      <c r="T117">
+        <v>7</v>
+      </c>
+      <c r="U117" s="4">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="V117" s="4">
+        <v>0.7742</v>
+      </c>
+      <c r="W117">
+        <v>70.933000000000007</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B118">
+        <v>8</v>
+      </c>
+      <c r="C118">
+        <v>1018</v>
+      </c>
+      <c r="D118">
+        <v>1031</v>
+      </c>
+      <c r="E118" t="s">
+        <v>23</v>
+      </c>
+      <c r="F118">
+        <v>100804</v>
+      </c>
+      <c r="G118">
+        <v>10</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>36906</v>
+      </c>
+      <c r="J118">
+        <v>471</v>
+      </c>
+      <c r="K118">
+        <v>17</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>15</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118" s="3">
+        <v>7.0601851851851847E-4</v>
+      </c>
+      <c r="P118" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="Q118" s="4">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="R118" s="4">
+        <v>3.61E-2</v>
+      </c>
+      <c r="S118" s="5">
+        <v>0</v>
+      </c>
+      <c r="T118">
+        <v>2</v>
+      </c>
+      <c r="U118" s="4">
+        <v>0.1176</v>
+      </c>
+      <c r="V118" s="4">
+        <v>0.59089999999999998</v>
+      </c>
+      <c r="W118">
+        <v>62.177</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B119">
+        <v>9</v>
+      </c>
+      <c r="C119">
+        <v>1018</v>
+      </c>
+      <c r="D119">
+        <v>1031</v>
+      </c>
+      <c r="E119" t="s">
+        <v>23</v>
+      </c>
+      <c r="F119">
+        <v>100804</v>
+      </c>
+      <c r="G119">
+        <v>10</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119">
+        <v>27485</v>
+      </c>
+      <c r="J119">
+        <v>253</v>
+      </c>
+      <c r="K119">
+        <v>8</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>8</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119" s="3">
+        <v>8.564814814814815E-4</v>
+      </c>
+      <c r="P119" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q119" s="4">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="R119" s="4">
+        <v>3.1600000000000003E-2</v>
+      </c>
+      <c r="S119" s="5">
+        <v>0</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119" s="5">
+        <v>0</v>
+      </c>
+      <c r="V119" s="4">
+        <v>1</v>
+      </c>
+      <c r="W119">
+        <v>44.084000000000003</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B120">
+        <v>10</v>
+      </c>
+      <c r="C120">
+        <v>1018</v>
+      </c>
+      <c r="D120">
+        <v>1031</v>
+      </c>
+      <c r="E120" t="s">
+        <v>23</v>
+      </c>
+      <c r="F120">
+        <v>100804</v>
+      </c>
+      <c r="G120">
+        <v>10</v>
+      </c>
+      <c r="H120">
+        <v>2</v>
+      </c>
+      <c r="I120">
+        <v>78003</v>
+      </c>
+      <c r="J120">
+        <v>739</v>
+      </c>
+      <c r="K120">
+        <v>27</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>26</v>
+      </c>
+      <c r="N120">
+        <v>3</v>
+      </c>
+      <c r="O120" s="3">
+        <v>9.1435185185185185E-4</v>
+      </c>
+      <c r="P120" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q120" s="4">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="R120" s="4">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="S120" s="5">
+        <v>0</v>
+      </c>
+      <c r="T120">
+        <v>1</v>
+      </c>
+      <c r="U120" s="4">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="V120" s="4">
+        <v>1</v>
+      </c>
+      <c r="W120">
+        <v>145.25800000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B121">
+        <v>11</v>
+      </c>
+      <c r="C121">
+        <v>1018</v>
+      </c>
+      <c r="D121">
+        <v>1031</v>
+      </c>
+      <c r="E121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121">
+        <v>100804</v>
+      </c>
+      <c r="G121">
+        <v>10</v>
+      </c>
+      <c r="H121">
+        <v>2</v>
+      </c>
+      <c r="I121">
+        <v>39415</v>
+      </c>
+      <c r="J121">
+        <v>418</v>
+      </c>
+      <c r="K121">
+        <v>22</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>20</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121" s="3">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="P121" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="Q121" s="4">
+        <v>1.06E-2</v>
+      </c>
+      <c r="R121" s="4">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="S121" s="5">
+        <v>0</v>
+      </c>
+      <c r="T121">
+        <v>2</v>
+      </c>
+      <c r="U121" s="4">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="V121" s="4">
+        <v>0.86960000000000004</v>
+      </c>
+      <c r="W121">
+        <v>70.561000000000007</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B122">
+        <v>12</v>
+      </c>
+      <c r="C122">
+        <v>1018</v>
+      </c>
+      <c r="D122">
+        <v>1031</v>
+      </c>
+      <c r="E122" t="s">
+        <v>23</v>
+      </c>
+      <c r="F122">
+        <v>100804</v>
+      </c>
+      <c r="G122">
+        <v>10</v>
+      </c>
+      <c r="H122">
+        <v>3</v>
+      </c>
+      <c r="I122">
+        <v>25318</v>
+      </c>
+      <c r="J122">
+        <v>296</v>
+      </c>
+      <c r="K122">
+        <v>21</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>16</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122" s="3">
+        <v>8.3333333333333339E-4</v>
+      </c>
+      <c r="P122" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="Q122" s="4">
+        <v>1.17E-2</v>
+      </c>
+      <c r="R122" s="4">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="S122" s="5">
+        <v>0</v>
+      </c>
+      <c r="T122">
+        <v>5</v>
+      </c>
+      <c r="U122" s="4">
+        <v>0.23810000000000001</v>
+      </c>
+      <c r="V122" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="W122">
+        <v>42.744</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B123">
+        <v>13</v>
+      </c>
+      <c r="C123">
+        <v>1018</v>
+      </c>
+      <c r="D123">
+        <v>1031</v>
+      </c>
+      <c r="E123" t="s">
+        <v>23</v>
+      </c>
+      <c r="F123">
+        <v>100804</v>
+      </c>
+      <c r="G123">
+        <v>10</v>
+      </c>
+      <c r="H123">
+        <v>3</v>
+      </c>
+      <c r="I123">
+        <v>38974</v>
+      </c>
+      <c r="J123">
+        <v>449</v>
+      </c>
+      <c r="K123">
+        <v>24</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>17</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="O123" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="P123" s="3">
+        <v>4.861111111111111E-4</v>
+      </c>
+      <c r="Q123" s="4">
+        <v>1.15E-2</v>
+      </c>
+      <c r="R123" s="4">
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="S123" s="5">
+        <v>0</v>
+      </c>
+      <c r="T123">
+        <v>7</v>
+      </c>
+      <c r="U123" s="4">
+        <v>0.29170000000000001</v>
+      </c>
+      <c r="V123" s="4">
+        <v>0.59260000000000002</v>
+      </c>
+      <c r="W123">
+        <v>67.712999999999994</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B124">
+        <v>14</v>
+      </c>
+      <c r="C124">
+        <v>1018</v>
+      </c>
+      <c r="D124">
+        <v>1031</v>
+      </c>
+      <c r="E124" t="s">
+        <v>23</v>
+      </c>
+      <c r="F124">
+        <v>100804</v>
+      </c>
+      <c r="G124">
+        <v>10</v>
+      </c>
+      <c r="H124">
+        <v>2</v>
+      </c>
+      <c r="I124">
+        <v>50787</v>
+      </c>
+      <c r="J124">
+        <v>486</v>
+      </c>
+      <c r="K124">
+        <v>17</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>17</v>
+      </c>
+      <c r="N124">
+        <v>2</v>
+      </c>
+      <c r="O124" s="3">
+        <v>9.3749999999999997E-4</v>
+      </c>
+      <c r="P124" s="3">
+        <v>6.134259259259259E-4</v>
+      </c>
+      <c r="Q124" s="4">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="R124" s="4">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="S124" s="5">
+        <v>0</v>
+      </c>
+      <c r="T124">
+        <v>0</v>
+      </c>
+      <c r="U124" s="5">
+        <v>0</v>
+      </c>
+      <c r="V124" s="4">
+        <v>0.78949999999999998</v>
+      </c>
+      <c r="W124">
+        <v>82.165000000000006</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B125">
+        <v>15</v>
+      </c>
+      <c r="C125">
+        <v>1018</v>
+      </c>
+      <c r="D125">
+        <v>1031</v>
+      </c>
+      <c r="E125" t="s">
+        <v>23</v>
+      </c>
+      <c r="F125">
+        <v>100804</v>
+      </c>
+      <c r="G125">
+        <v>10</v>
+      </c>
+      <c r="H125">
+        <v>3</v>
+      </c>
+      <c r="I125">
+        <v>61123</v>
+      </c>
+      <c r="J125">
+        <v>622</v>
+      </c>
+      <c r="K125">
+        <v>31</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>30</v>
+      </c>
+      <c r="N125">
+        <v>1</v>
+      </c>
+      <c r="O125" s="3">
+        <v>8.9120370370370373E-4</v>
+      </c>
+      <c r="P125" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="Q125" s="4">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="R125" s="4">
+        <v>4.9799999999999997E-2</v>
+      </c>
+      <c r="S125" s="5">
+        <v>0</v>
+      </c>
+      <c r="T125">
+        <v>1</v>
+      </c>
+      <c r="U125" s="4">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="V125" s="4">
+        <v>0.9032</v>
+      </c>
+      <c r="W125">
+        <v>91.131</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B126">
+        <v>16</v>
+      </c>
+      <c r="C126">
+        <v>1018</v>
+      </c>
+      <c r="D126">
+        <v>1031</v>
+      </c>
+      <c r="E126" t="s">
+        <v>23</v>
+      </c>
+      <c r="F126">
+        <v>100804</v>
+      </c>
+      <c r="G126">
+        <v>10</v>
+      </c>
+      <c r="H126">
+        <v>3</v>
+      </c>
+      <c r="I126">
+        <v>50360</v>
+      </c>
+      <c r="J126">
+        <v>603</v>
+      </c>
+      <c r="K126">
+        <v>24</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>18</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="P126" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="Q126" s="4">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R126" s="4">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="S126" s="5">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>6</v>
+      </c>
+      <c r="U126" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="V126" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="W126">
+        <v>83.765000000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B127">
+        <v>17</v>
+      </c>
+      <c r="C127">
+        <v>1018</v>
+      </c>
+      <c r="D127">
+        <v>1031</v>
+      </c>
+      <c r="E127" t="s">
+        <v>23</v>
+      </c>
+      <c r="F127">
+        <v>100804</v>
+      </c>
+      <c r="G127">
+        <v>10</v>
+      </c>
+      <c r="H127">
+        <v>2</v>
+      </c>
+      <c r="I127">
+        <v>34675</v>
+      </c>
+      <c r="J127">
+        <v>383</v>
+      </c>
+      <c r="K127">
+        <v>17</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>15</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127" s="3">
+        <v>8.7962962962962962E-4</v>
+      </c>
+      <c r="P127" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="Q127" s="4">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R127" s="4">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="S127" s="5">
+        <v>0</v>
+      </c>
+      <c r="T127">
+        <v>2</v>
+      </c>
+      <c r="U127" s="4">
+        <v>0.1176</v>
+      </c>
+      <c r="V127" s="4">
+        <v>0.6452</v>
+      </c>
+      <c r="W127">
+        <v>64.593000000000004</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B128">
+        <v>8</v>
+      </c>
+      <c r="C128">
+        <v>1018</v>
+      </c>
+      <c r="D128">
+        <v>1031</v>
+      </c>
+      <c r="E128" t="s">
+        <v>23</v>
+      </c>
+      <c r="F128">
+        <v>100539</v>
+      </c>
+      <c r="G128">
+        <v>10</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>36973</v>
+      </c>
+      <c r="J128">
+        <v>358</v>
+      </c>
+      <c r="K128">
+        <v>16</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>14</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128" s="3">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="P128" s="3">
+        <v>6.3657407407407413E-4</v>
+      </c>
+      <c r="Q128" s="4">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="R128" s="4">
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="S128" s="5">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>2</v>
+      </c>
+      <c r="U128" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="V128" s="4">
+        <v>0.64710000000000001</v>
+      </c>
+      <c r="W128">
+        <v>53.564999999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B129">
+        <v>9</v>
+      </c>
+      <c r="C129">
+        <v>1018</v>
+      </c>
+      <c r="D129">
+        <v>1031</v>
+      </c>
+      <c r="E129" t="s">
+        <v>23</v>
+      </c>
+      <c r="F129">
+        <v>100539</v>
+      </c>
+      <c r="G129">
+        <v>10</v>
+      </c>
+      <c r="H129">
+        <v>3</v>
+      </c>
+      <c r="I129">
+        <v>55450</v>
+      </c>
+      <c r="J129">
+        <v>394</v>
+      </c>
+      <c r="K129">
+        <v>19</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>19</v>
+      </c>
+      <c r="N129">
+        <v>1</v>
+      </c>
+      <c r="O129" s="3">
+        <v>1.1226851851851851E-3</v>
+      </c>
+      <c r="P129" s="3">
+        <v>6.7129629629629625E-4</v>
+      </c>
+      <c r="Q129" s="4">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="R129" s="4">
+        <v>4.82E-2</v>
+      </c>
+      <c r="S129" s="5">
+        <v>0</v>
+      </c>
+      <c r="T129">
+        <v>0</v>
+      </c>
+      <c r="U129" s="5">
+        <v>0</v>
+      </c>
+      <c r="V129" s="4">
+        <v>0.76919999999999999</v>
+      </c>
+      <c r="W129">
+        <v>76.850999999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B130">
+        <v>10</v>
+      </c>
+      <c r="C130">
+        <v>1018</v>
+      </c>
+      <c r="D130">
+        <v>1031</v>
+      </c>
+      <c r="E130" t="s">
+        <v>23</v>
+      </c>
+      <c r="F130">
+        <v>100539</v>
+      </c>
+      <c r="G130">
+        <v>10</v>
+      </c>
+      <c r="H130">
+        <v>3</v>
+      </c>
+      <c r="I130">
+        <v>72364</v>
+      </c>
+      <c r="J130">
+        <v>619</v>
+      </c>
+      <c r="K130">
+        <v>25</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>25</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130" s="3">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P130" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+      <c r="Q130" s="4">
+        <v>8.6E-3</v>
+      </c>
+      <c r="R130" s="4">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="S130" s="5">
+        <v>0</v>
+      </c>
+      <c r="T130">
+        <v>0</v>
+      </c>
+      <c r="U130" s="5">
+        <v>0</v>
+      </c>
+      <c r="V130" s="4">
+        <v>0.88460000000000005</v>
+      </c>
+      <c r="W130">
+        <v>101.087</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B131">
+        <v>11</v>
+      </c>
+      <c r="C131">
+        <v>1018</v>
+      </c>
+      <c r="D131">
+        <v>1031</v>
+      </c>
+      <c r="E131" t="s">
+        <v>23</v>
+      </c>
+      <c r="F131">
+        <v>100539</v>
+      </c>
+      <c r="G131">
+        <v>10</v>
+      </c>
+      <c r="H131">
+        <v>3</v>
+      </c>
+      <c r="I131">
+        <v>72669</v>
+      </c>
+      <c r="J131">
+        <v>657</v>
+      </c>
+      <c r="K131">
+        <v>27</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>27</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131" s="3">
+        <v>9.0277777777777774E-4</v>
+      </c>
+      <c r="P131" s="3">
+        <v>4.0509259259259258E-4</v>
+      </c>
+      <c r="Q131" s="4">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="R131" s="4">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="S131" s="5">
+        <v>0</v>
+      </c>
+      <c r="T131">
+        <v>0</v>
+      </c>
+      <c r="U131" s="5">
+        <v>0</v>
+      </c>
+      <c r="V131" s="4">
+        <v>0.96</v>
+      </c>
+      <c r="W131">
+        <v>103.435</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B132">
+        <v>12</v>
+      </c>
+      <c r="C132">
+        <v>1018</v>
+      </c>
+      <c r="D132">
+        <v>1031</v>
+      </c>
+      <c r="E132" t="s">
+        <v>23</v>
+      </c>
+      <c r="F132">
+        <v>100539</v>
+      </c>
+      <c r="G132">
+        <v>10</v>
+      </c>
+      <c r="H132">
+        <v>3</v>
+      </c>
+      <c r="I132">
+        <v>76625</v>
+      </c>
+      <c r="J132">
+        <v>555</v>
+      </c>
+      <c r="K132">
+        <v>18</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>17</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132" s="3">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="P132" s="3">
+        <v>4.6296296296296298E-4</v>
+      </c>
+      <c r="Q132" s="4">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R132" s="4">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="S132" s="5">
+        <v>0</v>
+      </c>
+      <c r="T132">
+        <v>1</v>
+      </c>
+      <c r="U132" s="4">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="V132" s="4">
+        <v>0.89470000000000005</v>
+      </c>
+      <c r="W132">
+        <v>89.097999999999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B133">
+        <v>13</v>
+      </c>
+      <c r="C133">
+        <v>1018</v>
+      </c>
+      <c r="D133">
+        <v>1031</v>
+      </c>
+      <c r="E133" t="s">
+        <v>23</v>
+      </c>
+      <c r="F133">
+        <v>100539</v>
+      </c>
+      <c r="G133">
+        <v>10</v>
+      </c>
+      <c r="H133">
+        <v>2</v>
+      </c>
+      <c r="I133">
+        <v>49365</v>
+      </c>
+      <c r="J133">
+        <v>281</v>
+      </c>
+      <c r="K133">
+        <v>12</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>12</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133" s="3">
+        <v>1.1689814814814816E-3</v>
+      </c>
+      <c r="P133" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="Q133" s="4">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="R133" s="4">
+        <v>4.2700000000000002E-2</v>
+      </c>
+      <c r="S133" s="5">
+        <v>0</v>
+      </c>
+      <c r="T133">
+        <v>0</v>
+      </c>
+      <c r="U133" s="5">
+        <v>0</v>
+      </c>
+      <c r="V133" s="4">
+        <v>1</v>
+      </c>
+      <c r="W133">
+        <v>40.478000000000002</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B134">
+        <v>14</v>
+      </c>
+      <c r="C134">
+        <v>1018</v>
+      </c>
+      <c r="D134">
+        <v>1031</v>
+      </c>
+      <c r="E134" t="s">
+        <v>23</v>
+      </c>
+      <c r="F134">
+        <v>100539</v>
+      </c>
+      <c r="G134">
+        <v>10</v>
+      </c>
+      <c r="H134">
+        <v>2</v>
+      </c>
+      <c r="I134">
+        <v>40164</v>
+      </c>
+      <c r="J134">
+        <v>567</v>
+      </c>
+      <c r="K134">
+        <v>16</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>14</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="P134" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="Q134" s="4">
+        <v>1.41E-2</v>
+      </c>
+      <c r="R134" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="S134" s="5">
+        <v>0</v>
+      </c>
+      <c r="T134">
+        <v>2</v>
+      </c>
+      <c r="U134" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="V134" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="W134">
+        <v>96.739000000000004</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B135">
+        <v>15</v>
+      </c>
+      <c r="C135">
+        <v>1018</v>
+      </c>
+      <c r="D135">
+        <v>1031</v>
+      </c>
+      <c r="E135" t="s">
+        <v>23</v>
+      </c>
+      <c r="F135">
+        <v>100539</v>
+      </c>
+      <c r="G135">
+        <v>10</v>
+      </c>
+      <c r="H135">
+        <v>3</v>
+      </c>
+      <c r="I135">
+        <v>51795</v>
+      </c>
+      <c r="J135">
+        <v>698</v>
+      </c>
+      <c r="K135">
+        <v>24</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>21</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135" s="3">
+        <v>7.1759259259259259E-4</v>
+      </c>
+      <c r="P135" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="Q135" s="4">
+        <v>1.35E-2</v>
+      </c>
+      <c r="R135" s="4">
+        <v>3.44E-2</v>
+      </c>
+      <c r="S135" s="5">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>3</v>
+      </c>
+      <c r="U135" s="4">
+        <v>0.125</v>
+      </c>
+      <c r="V135" s="4">
+        <v>0.95830000000000004</v>
+      </c>
+      <c r="W135">
+        <v>130.83699999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B136">
+        <v>16</v>
+      </c>
+      <c r="C136">
+        <v>1018</v>
+      </c>
+      <c r="D136">
+        <v>1031</v>
+      </c>
+      <c r="E136" t="s">
+        <v>23</v>
+      </c>
+      <c r="F136">
+        <v>100539</v>
+      </c>
+      <c r="G136">
+        <v>10</v>
+      </c>
+      <c r="H136">
+        <v>3</v>
+      </c>
+      <c r="I136">
+        <v>29771</v>
+      </c>
+      <c r="J136">
+        <v>265</v>
+      </c>
+      <c r="K136">
+        <v>14</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>9</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136" s="3">
+        <v>1.1805555555555556E-3</v>
+      </c>
+      <c r="P136" s="3">
+        <v>9.6064814814814819E-4</v>
+      </c>
+      <c r="Q136" s="4">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="R136" s="4">
+        <v>5.28E-2</v>
+      </c>
+      <c r="S136" s="5">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>5</v>
+      </c>
+      <c r="U136" s="4">
+        <v>0.35709999999999997</v>
+      </c>
+      <c r="V136" s="4">
+        <v>0.70830000000000004</v>
+      </c>
+      <c r="W136">
+        <v>75.789000000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B137">
+        <v>8</v>
+      </c>
+      <c r="C137">
+        <v>1018</v>
+      </c>
+      <c r="D137">
+        <v>1031</v>
+      </c>
+      <c r="E137" t="s">
+        <v>23</v>
+      </c>
+      <c r="F137">
+        <v>100536</v>
+      </c>
+      <c r="G137">
+        <v>10</v>
+      </c>
+      <c r="H137">
+        <v>1</v>
+      </c>
+      <c r="I137">
+        <v>38754</v>
+      </c>
+      <c r="J137">
+        <v>466</v>
+      </c>
+      <c r="K137">
+        <v>18</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>15</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="P137" s="3">
+        <v>1.3773148148148147E-3</v>
+      </c>
+      <c r="Q137" s="4">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R137" s="4">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="S137" s="5">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>3</v>
+      </c>
+      <c r="U137" s="4">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="V137" s="4">
+        <v>0.76470000000000005</v>
+      </c>
+      <c r="W137">
+        <v>96.787000000000006</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A138" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B138">
+        <v>9</v>
+      </c>
+      <c r="C138">
+        <v>1018</v>
+      </c>
+      <c r="D138">
+        <v>1031</v>
+      </c>
+      <c r="E138" t="s">
+        <v>23</v>
+      </c>
+      <c r="F138">
+        <v>100536</v>
+      </c>
+      <c r="G138">
+        <v>10</v>
+      </c>
+      <c r="H138">
+        <v>2</v>
+      </c>
+      <c r="I138">
+        <v>49798</v>
+      </c>
+      <c r="J138">
+        <v>369</v>
+      </c>
+      <c r="K138">
+        <v>9</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>9</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138" s="3">
+        <v>1.1342592592592593E-3</v>
+      </c>
+      <c r="P138" s="3">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="Q138" s="4">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="R138" s="4">
+        <v>2.4400000000000002E-2</v>
+      </c>
+      <c r="S138" s="5">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138" s="5">
+        <v>0</v>
+      </c>
+      <c r="V138" s="4">
+        <v>0.53849999999999998</v>
+      </c>
+      <c r="W138">
+        <v>82.959000000000003</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A139" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B139">
+        <v>10</v>
+      </c>
+      <c r="C139">
+        <v>1018</v>
+      </c>
+      <c r="D139">
+        <v>1031</v>
+      </c>
+      <c r="E139" t="s">
+        <v>23</v>
+      </c>
+      <c r="F139">
+        <v>100536</v>
+      </c>
+      <c r="G139">
+        <v>10</v>
+      </c>
+      <c r="H139">
+        <v>2</v>
+      </c>
+      <c r="I139">
+        <v>62711</v>
+      </c>
+      <c r="J139">
+        <v>453</v>
+      </c>
+      <c r="K139">
+        <v>16</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>16</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139" s="3">
+        <v>1.3078703703703703E-3</v>
+      </c>
+      <c r="P139" s="3">
+        <v>6.018518518518519E-4</v>
+      </c>
+      <c r="Q139" s="4">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R139" s="4">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="S139" s="5">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139" s="5">
+        <v>0</v>
+      </c>
+      <c r="V139" s="4">
+        <v>1</v>
+      </c>
+      <c r="W139">
+        <v>92.491</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A140" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B140">
+        <v>11</v>
+      </c>
+      <c r="C140">
+        <v>1018</v>
+      </c>
+      <c r="D140">
+        <v>1031</v>
+      </c>
+      <c r="E140" t="s">
+        <v>23</v>
+      </c>
+      <c r="F140">
+        <v>100536</v>
+      </c>
+      <c r="G140">
+        <v>10</v>
+      </c>
+      <c r="H140">
+        <v>3</v>
+      </c>
+      <c r="I140">
+        <v>56047</v>
+      </c>
+      <c r="J140">
+        <v>540</v>
+      </c>
+      <c r="K140">
+        <v>20</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>20</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="O140" s="3">
+        <v>9.4907407407407408E-4</v>
+      </c>
+      <c r="P140" s="3">
+        <v>7.6388888888888893E-4</v>
+      </c>
+      <c r="Q140" s="4">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="R140" s="4">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="S140" s="5">
+        <v>0</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140" s="5">
+        <v>0</v>
+      </c>
+      <c r="V140" s="4">
+        <v>0.95240000000000002</v>
+      </c>
+      <c r="W140">
+        <v>84.700999999999993</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A141" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B141">
+        <v>12</v>
+      </c>
+      <c r="C141">
+        <v>1018</v>
+      </c>
+      <c r="D141">
+        <v>1031</v>
+      </c>
+      <c r="E141" t="s">
+        <v>23</v>
+      </c>
+      <c r="F141">
+        <v>100536</v>
+      </c>
+      <c r="G141">
+        <v>10</v>
+      </c>
+      <c r="H141">
+        <v>3</v>
+      </c>
+      <c r="I141">
+        <v>53170</v>
+      </c>
+      <c r="J141">
+        <v>612</v>
+      </c>
+      <c r="K141">
+        <v>32</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>29</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="P141" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+      <c r="Q141" s="4">
+        <v>1.15E-2</v>
+      </c>
+      <c r="R141" s="4">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="S141" s="5">
+        <v>0</v>
+      </c>
+      <c r="T141">
+        <v>3</v>
+      </c>
+      <c r="U141" s="4">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="V141" s="4">
+        <v>0.9375</v>
+      </c>
+      <c r="W141">
+        <v>90.656000000000006</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B142">
+        <v>13</v>
+      </c>
+      <c r="C142">
+        <v>1018</v>
+      </c>
+      <c r="D142">
+        <v>1031</v>
+      </c>
+      <c r="E142" t="s">
+        <v>23</v>
+      </c>
+      <c r="F142">
+        <v>100536</v>
+      </c>
+      <c r="G142">
+        <v>10</v>
+      </c>
+      <c r="H142">
+        <v>2</v>
+      </c>
+      <c r="I142">
+        <v>39671</v>
+      </c>
+      <c r="J142">
+        <v>555</v>
+      </c>
+      <c r="K142">
+        <v>26</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>21</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="O142" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="P142" s="3">
+        <v>6.4814814814814813E-4</v>
+      </c>
+      <c r="Q142" s="4">
+        <v>1.4E-2</v>
+      </c>
+      <c r="R142" s="4">
+        <v>4.6800000000000001E-2</v>
+      </c>
+      <c r="S142" s="5">
+        <v>0</v>
+      </c>
+      <c r="T142">
+        <v>5</v>
+      </c>
+      <c r="U142" s="4">
+        <v>0.1923</v>
+      </c>
+      <c r="V142" s="4">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="W142">
+        <v>105.10299999999999</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A143" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B143">
+        <v>14</v>
+      </c>
+      <c r="C143">
+        <v>1018</v>
+      </c>
+      <c r="D143">
+        <v>1031</v>
+      </c>
+      <c r="E143" t="s">
+        <v>23</v>
+      </c>
+      <c r="F143">
+        <v>100536</v>
+      </c>
+      <c r="G143">
+        <v>10</v>
+      </c>
+      <c r="H143">
+        <v>3</v>
+      </c>
+      <c r="I143">
+        <v>40724</v>
+      </c>
+      <c r="J143">
+        <v>537</v>
+      </c>
+      <c r="K143">
+        <v>24</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>22</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143" s="3">
+        <v>7.7546296296296293E-4</v>
+      </c>
+      <c r="P143" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="Q143" s="4">
+        <v>1.32E-2</v>
+      </c>
+      <c r="R143" s="4">
+        <v>4.4699999999999997E-2</v>
+      </c>
+      <c r="S143" s="5">
+        <v>0</v>
+      </c>
+      <c r="T143">
+        <v>2</v>
+      </c>
+      <c r="U143" s="4">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="V143" s="4">
+        <v>0.58819999999999995</v>
+      </c>
+      <c r="W143">
+        <v>102.13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A144" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B144">
+        <v>15</v>
+      </c>
+      <c r="C144">
+        <v>1018</v>
+      </c>
+      <c r="D144">
+        <v>1031</v>
+      </c>
+      <c r="E144" t="s">
+        <v>23</v>
+      </c>
+      <c r="F144">
+        <v>100536</v>
+      </c>
+      <c r="G144">
+        <v>10</v>
+      </c>
+      <c r="H144">
+        <v>3</v>
+      </c>
+      <c r="I144">
+        <v>51926</v>
+      </c>
+      <c r="J144">
+        <v>469</v>
+      </c>
+      <c r="K144">
+        <v>29</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>28</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="O144" s="3">
+        <v>1.0185185185185184E-3</v>
+      </c>
+      <c r="P144" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="Q144" s="4">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="R144" s="4">
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="S144" s="5">
+        <v>0</v>
+      </c>
+      <c r="T144">
+        <v>1</v>
+      </c>
+      <c r="U144" s="4">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="V144" s="4">
+        <v>1</v>
+      </c>
+      <c r="W144">
+        <v>110.904</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A145" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B145">
+        <v>16</v>
+      </c>
+      <c r="C145">
+        <v>1018</v>
+      </c>
+      <c r="D145">
+        <v>1031</v>
+      </c>
+      <c r="E145" t="s">
+        <v>23</v>
+      </c>
+      <c r="F145">
+        <v>100536</v>
+      </c>
+      <c r="G145">
+        <v>10</v>
+      </c>
+      <c r="H145">
+        <v>3</v>
+      </c>
+      <c r="I145">
+        <v>44869</v>
+      </c>
+      <c r="J145">
+        <v>414</v>
+      </c>
+      <c r="K145">
+        <v>24</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>19</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" s="3">
+        <v>9.837962962962962E-4</v>
+      </c>
+      <c r="P145" s="3">
+        <v>7.407407407407407E-4</v>
+      </c>
+      <c r="Q145" s="4">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="R145" s="4">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="S145" s="5">
+        <v>0</v>
+      </c>
+      <c r="T145">
+        <v>5</v>
+      </c>
+      <c r="U145" s="4">
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="V145" s="4">
+        <v>0.72</v>
+      </c>
+      <c r="W145">
+        <v>86.66</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A146" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B146">
+        <v>17</v>
+      </c>
+      <c r="C146">
+        <v>1018</v>
+      </c>
+      <c r="D146">
+        <v>1031</v>
+      </c>
+      <c r="E146" t="s">
+        <v>23</v>
+      </c>
+      <c r="F146">
+        <v>100536</v>
+      </c>
+      <c r="G146">
+        <v>10</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+      <c r="I146">
+        <v>43872</v>
+      </c>
+      <c r="J146">
+        <v>528</v>
+      </c>
+      <c r="K146">
+        <v>23</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>18</v>
+      </c>
+      <c r="N146">
+        <v>1</v>
+      </c>
+      <c r="O146" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+      <c r="P146" s="3">
+        <v>1.0648148148148149E-3</v>
+      </c>
+      <c r="Q146" s="4">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R146" s="4">
+        <v>4.36E-2</v>
+      </c>
+      <c r="S146" s="5">
+        <v>0</v>
+      </c>
+      <c r="T146">
+        <v>5</v>
+      </c>
+      <c r="U146" s="4">
+        <v>0.21740000000000001</v>
+      </c>
+      <c r="V146" s="4">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="W146">
+        <v>95.248999999999995</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A147" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B147">
+        <v>8</v>
+      </c>
+      <c r="C147">
+        <v>1018</v>
+      </c>
+      <c r="D147">
+        <v>1031</v>
+      </c>
+      <c r="E147" t="s">
+        <v>23</v>
+      </c>
+      <c r="F147">
+        <v>100289</v>
+      </c>
+      <c r="G147">
+        <v>10</v>
+      </c>
+      <c r="H147">
+        <v>1</v>
+      </c>
+      <c r="I147">
+        <v>31290</v>
+      </c>
+      <c r="J147">
+        <v>512</v>
+      </c>
+      <c r="K147">
+        <v>17</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="M147">
+        <v>15</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="O147" s="3">
+        <v>5.3240740740740744E-4</v>
+      </c>
+      <c r="P147" s="3">
+        <v>5.4398148148148144E-4</v>
+      </c>
+      <c r="Q147" s="4">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="R147" s="4">
+        <v>3.32E-2</v>
+      </c>
+      <c r="S147" s="4">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="T147">
+        <v>1</v>
+      </c>
+      <c r="U147" s="4">
+        <v>6.25E-2</v>
+      </c>
+      <c r="V147" s="4">
+        <v>0.66669999999999996</v>
+      </c>
+      <c r="W147">
+        <v>40.872999999999998</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A148" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B148">
+        <v>9</v>
+      </c>
+      <c r="C148">
+        <v>1018</v>
+      </c>
+      <c r="D148">
+        <v>1031</v>
+      </c>
+      <c r="E148" t="s">
+        <v>23</v>
+      </c>
+      <c r="F148">
+        <v>100289</v>
+      </c>
+      <c r="G148">
+        <v>10</v>
+      </c>
+      <c r="H148">
+        <v>4</v>
+      </c>
+      <c r="I148">
+        <v>21390</v>
+      </c>
+      <c r="J148">
+        <v>500</v>
+      </c>
+      <c r="K148">
+        <v>17</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>17</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148" s="3">
+        <v>4.5138888888888887E-4</v>
+      </c>
+      <c r="P148" s="3">
+        <v>4.9768518518518521E-4</v>
+      </c>
+      <c r="Q148" s="4">
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="R148" s="4">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="S148" s="5">
+        <v>0</v>
+      </c>
+      <c r="T148">
+        <v>0</v>
+      </c>
+      <c r="U148" s="5">
+        <v>0</v>
+      </c>
+      <c r="V148" s="4">
+        <v>0.94120000000000004</v>
+      </c>
+      <c r="W148">
+        <v>0.88200000000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A149" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B149">
+        <v>10</v>
+      </c>
+      <c r="C149">
+        <v>1018</v>
+      </c>
+      <c r="D149">
+        <v>1031</v>
+      </c>
+      <c r="E149" t="s">
+        <v>23</v>
+      </c>
+      <c r="F149">
+        <v>100289</v>
+      </c>
+      <c r="G149">
+        <v>10</v>
+      </c>
+      <c r="H149">
+        <v>2</v>
+      </c>
+      <c r="I149">
+        <v>40724</v>
+      </c>
+      <c r="J149">
+        <v>714</v>
+      </c>
+      <c r="K149">
+        <v>26</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>24</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="P149" s="3">
+        <v>5.7870370370370367E-4</v>
+      </c>
+      <c r="Q149" s="4">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="R149" s="4">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="S149" s="5">
+        <v>0</v>
+      </c>
+      <c r="T149">
+        <v>2</v>
+      </c>
+      <c r="U149" s="4">
+        <v>7.6899999999999996E-2</v>
+      </c>
+      <c r="V149" s="4">
+        <v>0.92589999999999995</v>
+      </c>
+      <c r="W149">
+        <v>8.5749999999999993</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B150">
+        <v>11</v>
+      </c>
+      <c r="C150">
+        <v>1018</v>
+      </c>
+      <c r="D150">
+        <v>1031</v>
+      </c>
+      <c r="E150" t="s">
+        <v>23</v>
+      </c>
+      <c r="F150">
+        <v>100289</v>
+      </c>
+      <c r="G150">
+        <v>10</v>
+      </c>
+      <c r="H150">
+        <v>2</v>
+      </c>
+      <c r="I150">
+        <v>50872</v>
+      </c>
+      <c r="J150">
+        <v>973</v>
+      </c>
+      <c r="K150">
+        <v>28</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>27</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+      <c r="P150" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+      <c r="Q150" s="4">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="R150" s="4">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="S150" s="5">
+        <v>0</v>
+      </c>
+      <c r="T150">
+        <v>1</v>
+      </c>
+      <c r="U150" s="4">
+        <v>3.5700000000000003E-2</v>
+      </c>
+      <c r="V150" s="4">
+        <v>0.92589999999999995</v>
+      </c>
+      <c r="W150">
+        <v>48.040999999999997</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A151" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B151">
+        <v>12</v>
+      </c>
+      <c r="C151">
+        <v>1018</v>
+      </c>
+      <c r="D151">
+        <v>1031</v>
+      </c>
+      <c r="E151" t="s">
+        <v>23</v>
+      </c>
+      <c r="F151">
+        <v>100289</v>
+      </c>
+      <c r="G151">
+        <v>10</v>
+      </c>
+      <c r="H151">
+        <v>2</v>
+      </c>
+      <c r="I151">
+        <v>41816</v>
+      </c>
+      <c r="J151">
+        <v>458</v>
+      </c>
+      <c r="K151">
+        <v>12</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>12</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151" s="3">
+        <v>7.8703703703703705E-4</v>
+      </c>
+      <c r="P151" s="3">
+        <v>5.5555555555555556E-4</v>
+      </c>
+      <c r="Q151" s="4">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="R151" s="4">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="S151" s="5">
+        <v>0</v>
+      </c>
+      <c r="T151">
+        <v>0</v>
+      </c>
+      <c r="U151" s="5">
+        <v>0</v>
+      </c>
+      <c r="V151" s="4">
+        <v>0.65380000000000005</v>
+      </c>
+      <c r="W151">
+        <v>48.936999999999998</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B152">
+        <v>13</v>
+      </c>
+      <c r="C152">
+        <v>1018</v>
+      </c>
+      <c r="D152">
+        <v>1031</v>
+      </c>
+      <c r="E152" t="s">
+        <v>23</v>
+      </c>
+      <c r="F152">
+        <v>100289</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>623</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152" t="s">
+        <v>24</v>
+      </c>
+      <c r="P152" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q152" s="5">
+        <v>0</v>
+      </c>
+      <c r="R152" t="s">
+        <v>25</v>
+      </c>
+      <c r="S152" t="s">
+        <v>25</v>
+      </c>
+      <c r="T152">
+        <v>0</v>
+      </c>
+      <c r="U152" t="s">
+        <v>25</v>
+      </c>
+      <c r="V152" t="s">
+        <v>25</v>
+      </c>
+      <c r="W152">
+        <v>0.80500000000000005</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B153">
+        <v>14</v>
+      </c>
+      <c r="C153">
+        <v>1018</v>
+      </c>
+      <c r="D153">
+        <v>1031</v>
+      </c>
+      <c r="E153" t="s">
+        <v>23</v>
+      </c>
+      <c r="F153">
+        <v>100289</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>46312</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153" t="s">
+        <v>24</v>
+      </c>
+      <c r="P153" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q153" s="5">
+        <v>0</v>
+      </c>
+      <c r="R153" t="s">
+        <v>25</v>
+      </c>
+      <c r="S153" t="s">
+        <v>25</v>
+      </c>
+      <c r="T153">
+        <v>0</v>
+      </c>
+      <c r="U153" t="s">
+        <v>25</v>
+      </c>
+      <c r="V153" s="4">
+        <v>0.94440000000000002</v>
+      </c>
+      <c r="W153">
+        <v>101.892</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8521,7 +11787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35981261-B62C-4B92-BA64-8BAF4ABE5A4C}">
-  <dimension ref="A1:L726"/>
+  <dimension ref="A1:L750"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -33948,6 +37214,846 @@
       </c>
       <c r="L726" s="3">
         <v>2.199074074074074E-4</v>
+      </c>
+    </row>
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A727" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B727" t="s">
+        <v>32</v>
+      </c>
+      <c r="D727">
+        <v>9</v>
+      </c>
+      <c r="E727">
+        <v>226143</v>
+      </c>
+      <c r="F727">
+        <v>1221</v>
+      </c>
+      <c r="G727">
+        <v>858</v>
+      </c>
+      <c r="H727">
+        <v>8</v>
+      </c>
+      <c r="I727" s="4">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="J727" s="4">
+        <v>0.70269999999999999</v>
+      </c>
+      <c r="K727" s="4">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="L727" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A728" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B728" t="s">
+        <v>33</v>
+      </c>
+      <c r="D728">
+        <v>6</v>
+      </c>
+      <c r="E728">
+        <v>841</v>
+      </c>
+      <c r="F728">
+        <v>12</v>
+      </c>
+      <c r="G728">
+        <v>9</v>
+      </c>
+      <c r="H728">
+        <v>0</v>
+      </c>
+      <c r="I728" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="J728" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="K728" s="5">
+        <v>0</v>
+      </c>
+      <c r="L728" s="3">
+        <v>1.3888888888888889E-4</v>
+      </c>
+    </row>
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A729" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B729" t="s">
+        <v>34</v>
+      </c>
+      <c r="D729">
+        <v>7</v>
+      </c>
+      <c r="E729">
+        <v>178877</v>
+      </c>
+      <c r="F729">
+        <v>1395</v>
+      </c>
+      <c r="G729">
+        <v>1033</v>
+      </c>
+      <c r="H729">
+        <v>22</v>
+      </c>
+      <c r="I729" s="4">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="J729" s="4">
+        <v>0.74050000000000005</v>
+      </c>
+      <c r="K729" s="4">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="L729" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A730" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B730" t="s">
+        <v>35</v>
+      </c>
+      <c r="D730">
+        <v>9</v>
+      </c>
+      <c r="E730">
+        <v>173523</v>
+      </c>
+      <c r="F730">
+        <v>1389</v>
+      </c>
+      <c r="G730">
+        <v>967</v>
+      </c>
+      <c r="H730">
+        <v>22</v>
+      </c>
+      <c r="I730" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J730" s="4">
+        <v>0.69620000000000004</v>
+      </c>
+      <c r="K730" s="4">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="L730" s="3">
+        <v>2.8935185185185184E-4</v>
+      </c>
+    </row>
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A731" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B731" t="s">
+        <v>36</v>
+      </c>
+      <c r="D731">
+        <v>4</v>
+      </c>
+      <c r="E731">
+        <v>1379</v>
+      </c>
+      <c r="F731">
+        <v>14</v>
+      </c>
+      <c r="G731">
+        <v>12</v>
+      </c>
+      <c r="H731">
+        <v>0</v>
+      </c>
+      <c r="I731" s="4">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="J731" s="4">
+        <v>0.85709999999999997</v>
+      </c>
+      <c r="K731" s="5">
+        <v>0</v>
+      </c>
+      <c r="L731" s="3">
+        <v>1.4351851851851852E-3</v>
+      </c>
+    </row>
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A732" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B732" t="s">
+        <v>37</v>
+      </c>
+      <c r="D732">
+        <v>17</v>
+      </c>
+      <c r="E732">
+        <v>246</v>
+      </c>
+      <c r="F732">
+        <v>99</v>
+      </c>
+      <c r="G732">
+        <v>41</v>
+      </c>
+      <c r="H732">
+        <v>6</v>
+      </c>
+      <c r="I732" s="4">
+        <v>0.40239999999999998</v>
+      </c>
+      <c r="J732" s="4">
+        <v>0.41410000000000002</v>
+      </c>
+      <c r="K732" s="4">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="L732" s="3">
+        <v>3.9351851851851852E-4</v>
+      </c>
+    </row>
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A733" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B733" t="s">
+        <v>32</v>
+      </c>
+      <c r="D733">
+        <v>9</v>
+      </c>
+      <c r="E733">
+        <v>167414</v>
+      </c>
+      <c r="F733">
+        <v>1011</v>
+      </c>
+      <c r="G733">
+        <v>623</v>
+      </c>
+      <c r="H733">
+        <v>6</v>
+      </c>
+      <c r="I733" s="4">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J733" s="4">
+        <v>0.61619999999999997</v>
+      </c>
+      <c r="K733" s="4">
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="L733" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A734" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B734" t="s">
+        <v>33</v>
+      </c>
+      <c r="D734">
+        <v>4</v>
+      </c>
+      <c r="E734">
+        <v>715</v>
+      </c>
+      <c r="F734">
+        <v>5</v>
+      </c>
+      <c r="G734">
+        <v>5</v>
+      </c>
+      <c r="H734">
+        <v>1</v>
+      </c>
+      <c r="I734" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J734" s="5">
+        <v>1</v>
+      </c>
+      <c r="K734" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="L734" s="3">
+        <v>7.291666666666667E-4</v>
+      </c>
+    </row>
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A735" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B735" t="s">
+        <v>34</v>
+      </c>
+      <c r="D735">
+        <v>6</v>
+      </c>
+      <c r="E735">
+        <v>152217</v>
+      </c>
+      <c r="F735">
+        <v>1293</v>
+      </c>
+      <c r="G735">
+        <v>962</v>
+      </c>
+      <c r="H735">
+        <v>17</v>
+      </c>
+      <c r="I735" s="4">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="J735" s="4">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="K735" s="4">
+        <v>1.77E-2</v>
+      </c>
+      <c r="L735" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A736" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B736" t="s">
+        <v>35</v>
+      </c>
+      <c r="D736">
+        <v>9</v>
+      </c>
+      <c r="E736">
+        <v>190836</v>
+      </c>
+      <c r="F736">
+        <v>1721</v>
+      </c>
+      <c r="G736">
+        <v>1042</v>
+      </c>
+      <c r="H736">
+        <v>8</v>
+      </c>
+      <c r="I736" s="4">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="J736" s="4">
+        <v>0.60550000000000004</v>
+      </c>
+      <c r="K736" s="4">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="L736" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A737" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B737" t="s">
+        <v>36</v>
+      </c>
+      <c r="D737">
+        <v>5</v>
+      </c>
+      <c r="E737">
+        <v>1788</v>
+      </c>
+      <c r="F737">
+        <v>25</v>
+      </c>
+      <c r="G737">
+        <v>19</v>
+      </c>
+      <c r="H737">
+        <v>1</v>
+      </c>
+      <c r="I737" s="4">
+        <v>1.4E-2</v>
+      </c>
+      <c r="J737" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="K737" s="4">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="L737" s="3">
+        <v>5.2083333333333333E-4</v>
+      </c>
+    </row>
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A738" s="2">
+        <v>46196</v>
+      </c>
+      <c r="B738" t="s">
+        <v>37</v>
+      </c>
+      <c r="D738">
+        <v>15</v>
+      </c>
+      <c r="E738">
+        <v>219</v>
+      </c>
+      <c r="F738">
+        <v>107</v>
+      </c>
+      <c r="G738">
+        <v>29</v>
+      </c>
+      <c r="H738">
+        <v>8</v>
+      </c>
+      <c r="I738" s="4">
+        <v>0.48859999999999998</v>
+      </c>
+      <c r="J738" s="4">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="K738" s="4">
+        <v>0.27589999999999998</v>
+      </c>
+      <c r="L738" s="3">
+        <v>3.8194444444444446E-4</v>
+      </c>
+    </row>
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A739" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B739" t="s">
+        <v>32</v>
+      </c>
+      <c r="D739">
+        <v>10</v>
+      </c>
+      <c r="E739">
+        <v>240852</v>
+      </c>
+      <c r="F739">
+        <v>1147</v>
+      </c>
+      <c r="G739">
+        <v>782</v>
+      </c>
+      <c r="H739">
+        <v>3</v>
+      </c>
+      <c r="I739" s="4">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="J739" s="4">
+        <v>0.68179999999999996</v>
+      </c>
+      <c r="K739" s="4">
+        <v>3.8E-3</v>
+      </c>
+      <c r="L739" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+    </row>
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A740" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B740" t="s">
+        <v>33</v>
+      </c>
+      <c r="D740">
+        <v>1</v>
+      </c>
+      <c r="E740">
+        <v>64</v>
+      </c>
+      <c r="F740">
+        <v>1</v>
+      </c>
+      <c r="G740">
+        <v>1</v>
+      </c>
+      <c r="H740">
+        <v>0</v>
+      </c>
+      <c r="I740" s="4">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="J740" s="5">
+        <v>1</v>
+      </c>
+      <c r="K740" s="5">
+        <v>0</v>
+      </c>
+      <c r="L740" s="3">
+        <v>1.1574074074074075E-4</v>
+      </c>
+    </row>
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A741" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B741" t="s">
+        <v>34</v>
+      </c>
+      <c r="D741">
+        <v>7</v>
+      </c>
+      <c r="E741">
+        <v>223333</v>
+      </c>
+      <c r="F741">
+        <v>1745</v>
+      </c>
+      <c r="G741">
+        <v>1309</v>
+      </c>
+      <c r="H741">
+        <v>12</v>
+      </c>
+      <c r="I741" s="4">
+        <v>7.7999999999999996E-3</v>
+      </c>
+      <c r="J741" s="4">
+        <v>0.75009999999999999</v>
+      </c>
+      <c r="K741" s="4">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="L741" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A742" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B742" t="s">
+        <v>35</v>
+      </c>
+      <c r="D742">
+        <v>10</v>
+      </c>
+      <c r="E742">
+        <v>267068</v>
+      </c>
+      <c r="F742">
+        <v>1872</v>
+      </c>
+      <c r="G742">
+        <v>1227</v>
+      </c>
+      <c r="H742">
+        <v>20</v>
+      </c>
+      <c r="I742" s="4">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J742" s="4">
+        <v>0.65539999999999998</v>
+      </c>
+      <c r="K742" s="4">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="L742" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A743" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B743" t="s">
+        <v>36</v>
+      </c>
+      <c r="D743">
+        <v>6</v>
+      </c>
+      <c r="E743">
+        <v>1705</v>
+      </c>
+      <c r="F743">
+        <v>26</v>
+      </c>
+      <c r="G743">
+        <v>20</v>
+      </c>
+      <c r="H743">
+        <v>2</v>
+      </c>
+      <c r="I743" s="4">
+        <v>1.52E-2</v>
+      </c>
+      <c r="J743" s="4">
+        <v>0.76919999999999999</v>
+      </c>
+      <c r="K743" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="L743" s="3">
+        <v>6.5972222222222224E-4</v>
+      </c>
+    </row>
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A744" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B744" t="s">
+        <v>37</v>
+      </c>
+      <c r="D744">
+        <v>15</v>
+      </c>
+      <c r="E744">
+        <v>160</v>
+      </c>
+      <c r="F744">
+        <v>88</v>
+      </c>
+      <c r="G744">
+        <v>20</v>
+      </c>
+      <c r="H744">
+        <v>9</v>
+      </c>
+      <c r="I744" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J744" s="4">
+        <v>0.2273</v>
+      </c>
+      <c r="K744" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="L744" s="3">
+        <v>4.3981481481481481E-4</v>
+      </c>
+    </row>
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A745" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B745" t="s">
+        <v>32</v>
+      </c>
+      <c r="D745">
+        <v>10</v>
+      </c>
+      <c r="E745">
+        <v>218102</v>
+      </c>
+      <c r="F745">
+        <v>981</v>
+      </c>
+      <c r="G745">
+        <v>695</v>
+      </c>
+      <c r="H745">
+        <v>1</v>
+      </c>
+      <c r="I745" s="4">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="J745" s="4">
+        <v>0.70850000000000002</v>
+      </c>
+      <c r="K745" s="4">
+        <v>1.4E-3</v>
+      </c>
+      <c r="L745" s="3">
+        <v>2.6620370370370372E-4</v>
+      </c>
+    </row>
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A746" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B746" t="s">
+        <v>33</v>
+      </c>
+      <c r="D746">
+        <v>3</v>
+      </c>
+      <c r="E746">
+        <v>652</v>
+      </c>
+      <c r="F746">
+        <v>3</v>
+      </c>
+      <c r="G746">
+        <v>3</v>
+      </c>
+      <c r="H746">
+        <v>0</v>
+      </c>
+      <c r="I746" s="4">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="J746" s="5">
+        <v>1</v>
+      </c>
+      <c r="K746" s="5">
+        <v>0</v>
+      </c>
+      <c r="L746" s="3">
+        <v>2.4305555555555555E-4</v>
+      </c>
+    </row>
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A747" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B747" t="s">
+        <v>34</v>
+      </c>
+      <c r="D747">
+        <v>6</v>
+      </c>
+      <c r="E747">
+        <v>175281</v>
+      </c>
+      <c r="F747">
+        <v>1489</v>
+      </c>
+      <c r="G747">
+        <v>1114</v>
+      </c>
+      <c r="H747">
+        <v>13</v>
+      </c>
+      <c r="I747" s="4">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="J747" s="4">
+        <v>0.74819999999999998</v>
+      </c>
+      <c r="K747" s="4">
+        <v>1.17E-2</v>
+      </c>
+      <c r="L747" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A748" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B748" t="s">
+        <v>35</v>
+      </c>
+      <c r="D748">
+        <v>10</v>
+      </c>
+      <c r="E748">
+        <v>268360</v>
+      </c>
+      <c r="F748">
+        <v>1789</v>
+      </c>
+      <c r="G748">
+        <v>1263</v>
+      </c>
+      <c r="H748">
+        <v>11</v>
+      </c>
+      <c r="I748" s="4">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="J748" s="4">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="K748" s="4">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="L748" s="3">
+        <v>2.5462962962962961E-4</v>
+      </c>
+    </row>
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A749" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B749" t="s">
+        <v>36</v>
+      </c>
+      <c r="D749">
+        <v>5</v>
+      </c>
+      <c r="E749">
+        <v>1249</v>
+      </c>
+      <c r="F749">
+        <v>13</v>
+      </c>
+      <c r="G749">
+        <v>10</v>
+      </c>
+      <c r="H749">
+        <v>2</v>
+      </c>
+      <c r="I749" s="4">
+        <v>1.04E-2</v>
+      </c>
+      <c r="J749" s="4">
+        <v>0.76919999999999999</v>
+      </c>
+      <c r="K749" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="L749" s="3">
+        <v>1.4004629629629629E-3</v>
+      </c>
+    </row>
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A750" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B750" t="s">
+        <v>37</v>
+      </c>
+      <c r="D750">
+        <v>17</v>
+      </c>
+      <c r="E750">
+        <v>228</v>
+      </c>
+      <c r="F750">
+        <v>86</v>
+      </c>
+      <c r="G750">
+        <v>33</v>
+      </c>
+      <c r="H750">
+        <v>13</v>
+      </c>
+      <c r="I750" s="4">
+        <v>0.37719999999999998</v>
+      </c>
+      <c r="J750" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="K750" s="4">
+        <v>0.39389999999999997</v>
+      </c>
+      <c r="L750" s="3">
+        <v>3.7037037037037035E-4</v>
       </c>
     </row>
   </sheetData>
